--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,49 +465,49 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-11</t>
+          <t>Views_2026-04-12</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-12</t>
+          <t>Views_2026-04-14</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -534,202 +534,202 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1,951</t>
+          <t>1,956</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1,956</t>
+          <t>1,978</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>wFR_Ps8sLlI</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Never Lose Control When Someone Disrespects You</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wFR_Ps8sLlI</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>131</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A0x6fkcrix4</t>
+          <t>fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Never Defend Yourself Against Disrespect Here's Why</t>
+          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
+          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>khBEVHIzKEM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>Why Being YOURSELF Is Keeping You STUCK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fAEEc3xxmC8</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>571</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>586</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>ZJQ5tHebKPk</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>Why TRYING TO BE UNDERSTOOD After DISRESPECT Makes You Lose POWER</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=ZJQ5tHebKPk</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -756,268 +756,971 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Um_JjU7jfPo</t>
+          <t>DRQBvtISgH8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
+          <t>Public Humiliation Only Works If You React</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
+          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TgBjzPpNOwA</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>649</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>655</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AB5Tw2Yd4qE</t>
+          <t>A0x6fkcrix4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>When Your Point Gets Ignored, Don’t Repeat It—Say This (Stoic Rule)</t>
+          <t>Never Defend Yourself Against Disrespect Here's Why</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AB5Tw2Yd4qE</t>
+          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>93</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>98</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>wFR_Ps8sLlI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>Never Lose Control When Someone Disrespects You</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=wFR_Ps8sLlI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>NV2qQaDdxDM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>Every Time You KEEP THE PEACE After DISRESPECT, You Lose POWER</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=NV2qQaDdxDM</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>nvybbwOMwIA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Vye4llkNzwM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>qUd0X0Wn4-s</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>The Calm Response That Stops Rude People Fast</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C19SUX9jC1o</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>brLELECTtR8</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>UMpx0zHjbYs</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Why No One Respects You - The Daily Habits That Are Lowering Your VALUE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UMpx0zHjbYs</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Cxx0wy3mYzA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>How to Win People’s RESPECT Before You Say a Word</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Dt_r6f3nLIQ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Why No One RESPECTS You — You Keep Making DISRESPECT Cheap</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Dt_r6f3nLIQ</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>8yCYD0b2zsM</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Why EXPLAINING After DISRESPECT Makes You Look Weaker</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8yCYD0b2zsM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>b9Jj_A0dF4A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>If You React Like This, You Lose Respect Instantly</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=b9Jj_A0dF4A</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>wWnTzR023t8</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>How to Make People Respect You Without Chasing Anyone | Stoic Lessons</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wWnTzR023t8</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>QvJhQNdR-iU</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>9M1kjkk6oG8</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>pYH8XAZ8h0A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>agifyuQrXW8</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>B5ip0KwwVig</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>How To Command Respect As A Quiet Man | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=B5ip0KwwVig</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>41_ESKOfX-c</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>If You Don’t Respect Yourself, This Will Happen (Stoic Warning)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=41_ESKOfX-c</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>4,630</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>4,669</t>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>6,154</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>6,353</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -465,39 +465,39 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-12</t>
+          <t>Views_2026-04-14</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-14</t>
+          <t>Views_2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>zNiBsk4wAB4</t>
+          <t>SnJkoHJPREc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
+          <t>The Moment People Start Talking Over You</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
+          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>105</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>105</t>
         </is>
       </c>
     </row>
@@ -534,91 +534,91 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1,956</t>
+          <t>1,978</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1,978</t>
+          <t>2,008</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>cv9HlXnQozI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>The More You Let It Slide, The More They Push You</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>fAEEc3xxmC8</t>
+          <t>zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
+          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
+          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>55</t>
         </is>
       </c>
     </row>
@@ -645,17 +645,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -682,54 +682,54 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>586</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>596</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ZJQ5tHebKPk</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Why TRYING TO BE UNDERSTOOD After DISRESPECT Makes You Lose POWER</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZJQ5tHebKPk</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>131</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>141</t>
         </is>
       </c>
     </row>
@@ -756,113 +756,113 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DRQBvtISgH8</t>
+          <t>qUd0X0Wn4-s</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Public Humiliation Only Works If You React</t>
+          <t>The Calm Response That Stops Rude People Fast</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
+          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>193</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>How to Win People’s RESPECT Before You Say a Word</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>39</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A0x6fkcrix4</t>
+          <t>Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Never Defend Yourself Against Disrespect Here's Why</t>
+          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
+          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,71 +872,71 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Um_JjU7jfPo</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>229</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>wFR_Ps8sLlI</t>
+          <t>ZJQ5tHebKPk</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Never Lose Control When Someone Disrespects You</t>
+          <t>Why TRYING TO BE UNDERSTOOD After DISRESPECT Makes You Lose POWER</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wFR_Ps8sLlI</t>
+          <t>https://www.youtube.com/watch?v=ZJQ5tHebKPk</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -946,34 +946,34 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NV2qQaDdxDM</t>
+          <t>bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Every Time You KEEP THE PEACE After DISRESPECT, You Lose POWER</t>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NV2qQaDdxDM</t>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -983,34 +983,34 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>186</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>190</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>nvybbwOMwIA</t>
+          <t>DRQBvtISgH8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
+          <t>Public Humiliation Only Works If You React</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
+          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1020,34 +1020,34 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Vye4llkNzwM</t>
+          <t>agifyuQrXW8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1057,71 +1057,71 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>218</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>221</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>qUd0X0Wn4-s</t>
+          <t>A0x6fkcrix4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Calm Response That Stops Rude People Fast</t>
+          <t>Never Defend Yourself Against Disrespect Here's Why</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>98</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>100</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1131,34 +1131,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>655</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>657</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1168,34 +1168,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>390</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>392</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1205,123 +1205,123 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>324</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>326</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UMpx0zHjbYs</t>
+          <t>5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Why No One Respects You - The Daily Habits That Are Lowering Your VALUE</t>
+          <t>When They Try To Embarrass You, Do This</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=UMpx0zHjbYs</t>
+          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cxx0wy3mYzA</t>
+          <t>O-BjZNeGx94</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>How to Win People’s RESPECT Before You Say a Word</t>
+          <t>The Moment You REACT Too Fast, You Lose CONTROL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
+          <t>https://www.youtube.com/watch?v=O-BjZNeGx94</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dt_r6f3nLIQ</t>
+          <t>pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Why No One RESPECTS You — You Keep Making DISRESPECT Cheap</t>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Dt_r6f3nLIQ</t>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>111</t>
         </is>
       </c>
     </row>
@@ -1353,34 +1353,34 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>b9Jj_A0dF4A</t>
+          <t>fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>If You React Like This, You Lose Respect Instantly</t>
+          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=b9Jj_A0dF4A</t>
+          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1390,34 +1390,34 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>wWnTzR023t8</t>
+          <t>Dt_r6f3nLIQ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>How to Make People Respect You Without Chasing Anyone | Stoic Lessons</t>
+          <t>Why No One RESPECTS You — You Keep Making DISRESPECT Cheap</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wWnTzR023t8</t>
+          <t>https://www.youtube.com/watch?v=Dt_r6f3nLIQ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1427,34 +1427,34 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>wFR_Ps8sLlI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>Never Lose Control When Someone Disrespects You</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=wFR_Ps8sLlI</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1464,34 +1464,34 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>64</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>65</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>QvJhQNdR-iU</t>
+          <t>wWnTzR023t8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
+          <t>How to Make People Respect You Without Chasing Anyone | Stoic Lessons</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
+          <t>https://www.youtube.com/watch?v=wWnTzR023t8</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>Vye4llkNzwM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1538,34 +1538,34 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>65</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pYH8XAZ8h0A</t>
+          <t>nvybbwOMwIA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1575,34 +1575,34 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>64</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>65</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>agifyuQrXW8</t>
+          <t>2OilqvW_HzY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1612,34 +1612,34 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>269</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>270</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B5ip0KwwVig</t>
+          <t>p_Z683xxqfs</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>How To Command Respect As A Quiet Man | Stoic Wisdom</t>
+          <t>Always Available? That’s Why They Don’t Respect You (5 Stoic Rules)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B5ip0KwwVig</t>
+          <t>https://www.youtube.com/watch?v=p_Z683xxqfs</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>76</t>
         </is>
       </c>
     </row>
@@ -1686,12 +1686,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>97</t>
         </is>
       </c>
     </row>
@@ -1710,17 +1710,17 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>293</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>6,154</t>
+          <t>6,216</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>6,353</t>
+          <t>6,509</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-14</t>
+          <t>Views_2026-04-16</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-16</t>
+          <t>Views_2026-04-17</t>
         </is>
       </c>
     </row>
@@ -497,387 +497,387 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>151</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>cv9HlXnQozI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>The More You Let It Slide, The More They Push You</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1,978</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2,008</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cv9HlXnQozI</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The More You Let It Slide, The More They Push You</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2,008</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2,022</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>zNiBsk4wAB4</t>
+          <t>cNyqLV3GFq8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
+          <t>The More You Explain Your NO, The Less They Respect It</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
+          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>khBEVHIzKEM</t>
+          <t>Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Why Being YOURSELF Is Keeping You STUCK</t>
+          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
+          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>53</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>khBEVHIzKEM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>Why Being YOURSELF Is Keeping You STUCK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>657</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>662</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>qtid1KrxsOg</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Real Mistake After DISRESPECT Is Trying to PROVE Yourself</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qtid1KrxsOg</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>392</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>395</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>qUd0X0Wn4-s</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Calm Response That Stops Rude People Fast</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>326</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>329</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cxx0wy3mYzA</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>How to Win People’s RESPECT Before You Say a Word</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>335</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>338</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Um_JjU7jfPo</t>
+          <t>ZJQ5tHebKPk</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
+          <t>Why TRYING TO BE UNDERSTOOD After DISRESPECT Makes You Lose POWER</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
+          <t>https://www.youtube.com/watch?v=ZJQ5tHebKPk</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>39</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -904,446 +904,446 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>231</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ZJQ5tHebKPk</t>
+          <t>qtid1KrxsOg</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Why TRYING TO BE UNDERSTOOD After DISRESPECT Makes You Lose POWER</t>
+          <t>The Real Mistake After DISRESPECT Is Trying to PROVE Yourself</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZJQ5tHebKPk</t>
+          <t>https://www.youtube.com/watch?v=qtid1KrxsOg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>O-BjZNeGx94</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+          <t>The Moment You REACT Too Fast, You Lose CONTROL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+          <t>https://www.youtube.com/watch?v=O-BjZNeGx94</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DRQBvtISgH8</t>
+          <t>agifyuQrXW8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Public Humiliation Only Works If You React</t>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>223</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>agifyuQrXW8</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>596</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>598</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A0x6fkcrix4</t>
+          <t>QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Never Defend Yourself Against Disrespect Here's Why</t>
+          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
+          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>58</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>59</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>Dt_r6f3nLIQ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>Why No One RESPECTS You — You Keep Making DISRESPECT Cheap</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=Dt_r6f3nLIQ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>77</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>UMpx0zHjbYs</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>Why No One Respects You - The Daily Habits That Are Lowering Your VALUE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=UMpx0zHjbYs</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>A0x6fkcrix4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>Never Defend Yourself Against Disrespect Here's Why</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>101</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5Ydh9Xglz9s</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>When They Try To Embarrass You, Do This</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>141</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>142</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>O-BjZNeGx94</t>
+          <t>uyK1jiL9Hek</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Moment You REACT Too Fast, You Lose CONTROL</t>
+          <t>Why One INSULT Can Ruin Your Entire Day</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=O-BjZNeGx94</t>
+          <t>https://www.youtube.com/watch?v=uyK1jiL9Hek</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pYH8XAZ8h0A</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8yCYD0b2zsM</t>
+          <t>g54e8p6ylts</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Why EXPLAINING After DISRESPECT Makes You Look Weaker</t>
+          <t>That “Quick Favor” Is Why They Disrespect You</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8yCYD0b2zsM</t>
+          <t>https://www.youtube.com/watch?v=g54e8p6ylts</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1353,34 +1353,34 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fAEEc3xxmC8</t>
+          <t>Vye4llkNzwM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1390,34 +1390,34 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>66</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dt_r6f3nLIQ</t>
+          <t>nvybbwOMwIA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Why No One RESPECTS You — You Keep Making DISRESPECT Cheap</t>
+          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Dt_r6f3nLIQ</t>
+          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1427,34 +1427,34 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>65</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>wFR_Ps8sLlI</t>
+          <t>pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Never Lose Control When Someone Disrespects You</t>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wFR_Ps8sLlI</t>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1464,34 +1464,34 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>111</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>112</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>wWnTzR023t8</t>
+          <t>AB5Tw2Yd4qE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>How to Make People Respect You Without Chasing Anyone | Stoic Lessons</t>
+          <t>When Your Point Gets Ignored, Don’t Repeat It—Say This (Stoic Rule)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wWnTzR023t8</t>
+          <t>https://www.youtube.com/watch?v=AB5Tw2Yd4qE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Vye4llkNzwM</t>
+          <t>TH331d5OGVs</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+          <t>Disrespected in a Meeting? Do This (Stoic 30-Second Rule)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+          <t>https://www.youtube.com/watch?v=TH331d5OGVs</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1538,34 +1538,34 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>nvybbwOMwIA</t>
+          <t>nSSLusuBoC8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
+          <t>SET BOUNDARIES, GAIN RESPECT: 5 STOIC RULES (For People Who Get WALKED OVER)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
+          <t>https://www.youtube.com/watch?v=nSSLusuBoC8</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1575,34 +1575,34 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2OilqvW_HzY</t>
+          <t>0w4OAOyEEUE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+          <t>When They Interrupt You, Do This in 3 Seconds (Stoic)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+          <t>https://www.youtube.com/watch?v=0w4OAOyEEUE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1612,34 +1612,34 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>131</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>132</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>p_Z683xxqfs</t>
+          <t>FqpFUsYO-AQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Always Available? That’s Why They Don’t Respect You (5 Stoic Rules)</t>
+          <t>6 Reasons No One Takes You Seriously (Stoic Self-Respect Advice)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=p_Z683xxqfs</t>
+          <t>https://www.youtube.com/watch?v=FqpFUsYO-AQ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1649,34 +1649,34 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>167</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>168</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>41_ESKOfX-c</t>
+          <t>IKtI1Kc9YC8</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>If You Don’t Respect Yourself, This Will Happen (Stoic Warning)</t>
+          <t>You’re Not Kind — You’re Being Used (5 Stoic Truths)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=41_ESKOfX-c</t>
+          <t>https://www.youtube.com/watch?v=IKtI1Kc9YC8</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1686,41 +1686,226 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>BypRuE0bqNg</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>If They Don’t Respect You, Walk Away (5 Seneca Rules)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BypRuE0bqNg</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1A1bXruIgD4</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Disrespected? These 10 Manipulative Phrases Make You Apologize (Stoic Replies)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1A1bXruIgD4</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>GO53yD8kmuY</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>13 Signs You're Being DISRESPECTED and Need to Take Action Now</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GO53yD8kmuY</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>5IXlofJxEUg</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>When Someone Ignores You, Walk Away With Dignity (Stoic Guide)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5IXlofJxEUg</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>6,216</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>6,509</t>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>6,914</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>7,063</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-16</t>
+          <t>Views_2026-04-17</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-17</t>
+          <t>Views_2026-04-18</t>
         </is>
       </c>
     </row>
@@ -497,91 +497,91 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>151</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>165</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cv9HlXnQozI</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The More You Let It Slide, The More They Push You</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2,022</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>2,034</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2,008</t>
+          <t>598</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2,022</t>
+          <t>605</t>
         </is>
       </c>
     </row>
@@ -608,261 +608,261 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Um_JjU7jfPo</t>
+          <t>qtid1KrxsOg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
+          <t>The Real Mistake After DISRESPECT Is Trying to PROVE Yourself</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
+          <t>https://www.youtube.com/watch?v=qtid1KrxsOg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>khBEVHIzKEM</t>
+          <t>WFY6UCmgi74</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Why Being YOURSELF Is Keeping You STUCK</t>
+          <t>Why Talking More Makes You Sound LESS Important</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
+          <t>https://www.youtube.com/watch?v=WFY6UCmgi74</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>395</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>399</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>cv9HlXnQozI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>The More You Let It Slide, The More They Push You</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>662</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>664</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>DRQBvtISgH8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>Public Humiliation Only Works If You React</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ZJQ5tHebKPk</t>
+          <t>Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Why TRYING TO BE UNDERSTOOD After DISRESPECT Makes You Lose POWER</t>
+          <t>How to Win People’s RESPECT Before You Say a Word</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZJQ5tHebKPk</t>
+          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,219 +872,219 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>53</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>qtid1KrxsOg</t>
+          <t>Dt_r6f3nLIQ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Real Mistake After DISRESPECT Is Trying to PROVE Yourself</t>
+          <t>Why No One RESPECTS You — You Keep Making DISRESPECT Cheap</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qtid1KrxsOg</t>
+          <t>https://www.youtube.com/watch?v=Dt_r6f3nLIQ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>78</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O-BjZNeGx94</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Moment You REACT Too Fast, You Lose CONTROL</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=O-BjZNeGx94</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>142</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>143</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>agifyuQrXW8</t>
+          <t>NV2qQaDdxDM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+          <t>Every Time You KEEP THE PEACE After DISRESPECT, You Lose POWER</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+          <t>https://www.youtube.com/watch?v=NV2qQaDdxDM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>QvJhQNdR-iU</t>
+          <t>qUd0X0Wn4-s</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
+          <t>The Calm Response That Stops Rude People Fast</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
+          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1094,34 +1094,34 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>194</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dt_r6f3nLIQ</t>
+          <t>bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Why No One RESPECTS You — You Keep Making DISRESPECT Cheap</t>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Dt_r6f3nLIQ</t>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1131,34 +1131,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>192</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UMpx0zHjbYs</t>
+          <t>5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Why No One Respects You - The Daily Habits That Are Lowering Your VALUE</t>
+          <t>When They Try To Embarrass You, Do This</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=UMpx0zHjbYs</t>
+          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1168,34 +1168,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A0x6fkcrix4</t>
+          <t>nvybbwOMwIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Never Defend Yourself Against Disrespect Here's Why</t>
+          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
+          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1205,707 +1205,41 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>66</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>4,835</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>142</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>uyK1jiL9Hek</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Why One INSULT Can Ruin Your Entire Day</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=uyK1jiL9Hek</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>g54e8p6ylts</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>That “Quick Favor” Is Why They Disrespect You</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=g54e8p6ylts</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Vye4llkNzwM</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>nvybbwOMwIA</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>pYH8XAZ8h0A</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>AB5Tw2Yd4qE</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>When Your Point Gets Ignored, Don’t Repeat It—Say This (Stoic Rule)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=AB5Tw2Yd4qE</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-01-04</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TH331d5OGVs</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Disrespected in a Meeting? Do This (Stoic 30-Second Rule)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=TH331d5OGVs</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2025-12-25</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>nSSLusuBoC8</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>SET BOUNDARIES, GAIN RESPECT: 5 STOIC RULES (For People Who Get WALKED OVER)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=nSSLusuBoC8</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>0w4OAOyEEUE</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>When They Interrupt You, Do This in 3 Seconds (Stoic)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=0w4OAOyEEUE</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>FqpFUsYO-AQ</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>6 Reasons No One Takes You Seriously (Stoic Self-Respect Advice)</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=FqpFUsYO-AQ</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>IKtI1Kc9YC8</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>You’re Not Kind — You’re Being Used (5 Stoic Truths)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=IKtI1Kc9YC8</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>BypRuE0bqNg</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>If They Don’t Respect You, Walk Away (5 Seneca Rules)</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=BypRuE0bqNg</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>1A1bXruIgD4</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Disrespected? These 10 Manipulative Phrases Make You Apologize (Stoic Replies)</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=1A1bXruIgD4</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2025-12-24</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>bMVVPaC5TNc</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>GO53yD8kmuY</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>13 Signs You're Being DISRESPECTED and Need to Take Action Now</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=GO53yD8kmuY</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>5IXlofJxEUg</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>When Someone Ignores You, Walk Away With Dignity (Stoic Guide)</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5IXlofJxEUg</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>6,914</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>7,063</t>
+          <t>4,903</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,293 +465,293 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-17</t>
+          <t>Views_2026-04-18</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-18</t>
+          <t>Views_2026-04-19</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SnJkoHJPREc</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Moment People Start Talking Over You</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>2,034</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>2,045</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>WFY6UCmgi74</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>Why Talking More Makes You Sound LESS Important</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=WFY6UCmgi74</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2,022</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2,034</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>SnJkoHJPREc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>The Moment People Start Talking Over You</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>165</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cNyqLV3GFq8</t>
+          <t>C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The More You Explain Your NO, The Less They Respect It</t>
+          <t>The Moment Your Plans Start Sounding Empty</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
+          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>qtid1KrxsOg</t>
+          <t>Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Real Mistake After DISRESPECT Is Trying to PROVE Yourself</t>
+          <t>How to Win People’s RESPECT Before You Say a Word</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qtid1KrxsOg</t>
+          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WFY6UCmgi74</t>
+          <t>cNyqLV3GFq8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Why Talking More Makes You Sound LESS Important</t>
+          <t>The More You Explain Your NO, The Less They Respect It</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=WFY6UCmgi74</t>
+          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>605</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>608</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cv9HlXnQozI</t>
+          <t>zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The More You Let It Slide, The More They Push You</t>
+          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
+          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -761,34 +761,34 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -798,34 +798,34 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>399</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>401</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DRQBvtISgH8</t>
+          <t>fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Public Humiliation Only Works If You React</t>
+          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
+          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -835,34 +835,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cxx0wy3mYzA</t>
+          <t>uyK1jiL9Hek</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>How to Win People’s RESPECT Before You Say a Word</t>
+          <t>Why One INSULT Can Ruin Your Entire Day</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
+          <t>https://www.youtube.com/watch?v=uyK1jiL9Hek</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,108 +872,108 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>zNiBsk4wAB4</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>664</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>666</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dt_r6f3nLIQ</t>
+          <t>ZJQ5tHebKPk</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Why No One RESPECTS You — You Keep Making DISRESPECT Cheap</t>
+          <t>Why TRYING TO BE UNDERSTOOD After DISRESPECT Makes You Lose POWER</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Dt_r6f3nLIQ</t>
+          <t>https://www.youtube.com/watch?v=ZJQ5tHebKPk</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>khBEVHIzKEM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>Why Being YOURSELF Is Keeping You STUCK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -983,34 +983,34 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>39</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NV2qQaDdxDM</t>
+          <t>8yCYD0b2zsM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Every Time You KEEP THE PEACE After DISRESPECT, You Lose POWER</t>
+          <t>Why EXPLAINING After DISRESPECT Makes You Look Weaker</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NV2qQaDdxDM</t>
+          <t>https://www.youtube.com/watch?v=8yCYD0b2zsM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1020,34 +1020,34 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Um_JjU7jfPo</t>
+          <t>NV2qQaDdxDM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
+          <t>Every Time You KEEP THE PEACE After DISRESPECT, You Lose POWER</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
+          <t>https://www.youtube.com/watch?v=NV2qQaDdxDM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1057,34 +1057,34 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>qUd0X0Wn4-s</t>
+          <t>DRQBvtISgH8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Calm Response That Stops Rude People Fast</t>
+          <t>Public Humiliation Only Works If You React</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1094,34 +1094,34 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1131,34 +1131,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5Ydh9Xglz9s</t>
+          <t>qUd0X0Wn4-s</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>When They Try To Embarrass You, Do This</t>
+          <t>The Calm Response That Stops Rude People Fast</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
+          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1168,34 +1168,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>194</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>195</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>nvybbwOMwIA</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1205,41 +1205,115 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>TgBjzPpNOwA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Vye4llkNzwM</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>4,835</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>4,903</t>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4,670</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>4,726</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,663 +465,663 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-18</t>
+          <t>Views_2026-04-19</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-19</t>
+          <t>Views_2026-04-21</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>Why Your NO Starts Sounding Like a MAYBE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,034</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,045</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WFY6UCmgi74</t>
+          <t>hikgGDBJWiU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why Talking More Makes You Sound LESS Important</t>
+          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=WFY6UCmgi74</t>
+          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SnJkoHJPREc</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Moment People Start Talking Over You</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>2,045</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>2,059</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C2ZZh6r6afI</t>
+          <t>zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Moment Your Plans Start Sounding Empty</t>
+          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
+          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cxx0wy3mYzA</t>
+          <t>DRQBvtISgH8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>How to Win People’s RESPECT Before You Say a Word</t>
+          <t>Public Humiliation Only Works If You React</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
+          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cNyqLV3GFq8</t>
+          <t>khBEVHIzKEM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The More You Explain Your NO, The Less They Respect It</t>
+          <t>Why Being YOURSELF Is Keeping You STUCK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
+          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>How to Win People’s RESPECT Before You Say a Word</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>zNiBsk4wAB4</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>608</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>613</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>ZJQ5tHebKPk</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>Why TRYING TO BE UNDERSTOOD After DISRESPECT Makes You Lose POWER</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=ZJQ5tHebKPk</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fAEEc3xxmC8</t>
+          <t>cv9HlXnQozI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
+          <t>The More You Let It Slide, The More They Push You</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
+          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>uyK1jiL9Hek</t>
+          <t>fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Why One INSULT Can Ruin Your Entire Day</t>
+          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uyK1jiL9Hek</t>
+          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>WFY6UCmgi74</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>Why Talking More Makes You Sound LESS Important</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=WFY6UCmgi74</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ZJQ5tHebKPk</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Why TRYING TO BE UNDERSTOOD After DISRESPECT Makes You Lose POWER</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZJQ5tHebKPk</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>329</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>332</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>khBEVHIzKEM</t>
+          <t>Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Why Being YOURSELF Is Keeping You STUCK</t>
+          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
+          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>58</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8yCYD0b2zsM</t>
+          <t>cNyqLV3GFq8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Why EXPLAINING After DISRESPECT Makes You Look Weaker</t>
+          <t>The More You Explain Your NO, The Less They Respect It</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8yCYD0b2zsM</t>
+          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NV2qQaDdxDM</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Every Time You KEEP THE PEACE After DISRESPECT, You Lose POWER</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NV2qQaDdxDM</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>338</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>340</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DRQBvtISgH8</t>
+          <t>A0x6fkcrix4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Public Humiliation Only Works If You React</t>
+          <t>Never Defend Yourself Against Disrespect Here's Why</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
+          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>103</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Um_JjU7jfPo</t>
+          <t>C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
+          <t>The Moment Your Plans Start Sounding Empty</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
+          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1131,34 +1131,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>qUd0X0Wn4-s</t>
+          <t>SnJkoHJPREc</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Calm Response That Stops Rude People Fast</t>
+          <t>The Moment People Start Talking Over You</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1168,34 +1168,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>170</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>171</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>qtid1KrxsOg</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>The Real Mistake After DISRESPECT Is Trying to PROVE Yourself</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=qtid1KrxsOg</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1205,34 +1205,34 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TgBjzPpNOwA</t>
+          <t>UMpx0zHjbYs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+          <t>Why No One Respects You - The Daily Habits That Are Lowering Your VALUE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+          <t>https://www.youtube.com/watch?v=UMpx0zHjbYs</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1242,34 +1242,34 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>56</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Vye4llkNzwM</t>
+          <t>Dt_r6f3nLIQ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+          <t>Why No One RESPECTS You — You Keep Making DISRESPECT Cheap</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+          <t>https://www.youtube.com/watch?v=Dt_r6f3nLIQ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1279,41 +1279,263 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>b9Jj_A0dF4A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>If You React Like This, You Lose Respect Instantly</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=b9Jj_A0dF4A</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>5u_0LFn95ec</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TgBjzPpNOwA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>brLELECTtR8</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>4,670</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>4,726</t>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>5,657</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>5,770</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,530 +465,530 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-19</t>
+          <t>Views_2026-04-21</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-21</t>
+          <t>Views_2026-04-22</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7V5HQ-od-c4</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Why Your NO Starts Sounding Like a MAYBE</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2,059</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2,076</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hikgGDBJWiU</t>
+          <t>7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
+          <t>Why Your NO Starts Sounding Like a MAYBE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
+          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>hikgGDBJWiU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2,045</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2,059</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>zNiBsk4wAB4</t>
+          <t>ZJQ5tHebKPk</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
+          <t>Why TRYING TO BE UNDERSTOOD After DISRESPECT Makes You Lose POWER</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
+          <t>https://www.youtube.com/watch?v=ZJQ5tHebKPk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>53</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DRQBvtISgH8</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Public Humiliation Only Works If You React</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>613</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>618</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>khBEVHIzKEM</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Why Being YOURSELF Is Keeping You STUCK</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>406</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cxx0wy3mYzA</t>
+          <t>khBEVHIzKEM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>How to Win People’s RESPECT Before You Say a Word</t>
+          <t>Why Being YOURSELF Is Keeping You STUCK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
+          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>The Moment Your Plans Start Sounding Empty</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ZJQ5tHebKPk</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Why TRYING TO BE UNDERSTOOD After DISRESPECT Makes You Lose POWER</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZJQ5tHebKPk</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>332</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>334</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cv9HlXnQozI</t>
+          <t>DRQBvtISgH8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The More You Let It Slide, The More They Push You</t>
+          <t>Public Humiliation Only Works If You React</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
+          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fAEEc3xxmC8</t>
+          <t>cv9HlXnQozI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
+          <t>The More You Let It Slide, The More They Push You</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
+          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>56</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WFY6UCmgi74</t>
+          <t>SnJkoHJPREc</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Why Talking More Makes You Sound LESS Important</t>
+          <t>The Moment People Start Talking Over You</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=WFY6UCmgi74</t>
+          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>171</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>173</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>667</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>669</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Um_JjU7jfPo</t>
+          <t>DZ0NL1qMM8A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
+          <t>The “JUST JOKING” Follow-Up Is the REAL Test</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
+          <t>https://www.youtube.com/watch?v=DZ0NL1qMM8A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1015,113 +1015,113 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A0x6fkcrix4</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Never Defend Yourself Against Disrespect Here's Why</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>77</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C2ZZh6r6afI</t>
+          <t>NV2qQaDdxDM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Moment Your Plans Start Sounding Empty</t>
+          <t>Every Time You KEEP THE PEACE After DISRESPECT, You Lose POWER</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
+          <t>https://www.youtube.com/watch?v=NV2qQaDdxDM</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1131,34 +1131,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SnJkoHJPREc</t>
+          <t>Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Moment People Start Talking Over You</t>
+          <t>How to Win People’s RESPECT Before You Say a Word</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1168,34 +1168,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>qtid1KrxsOg</t>
+          <t>Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Real Mistake After DISRESPECT Is Trying to PROVE Yourself</t>
+          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qtid1KrxsOg</t>
+          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1205,34 +1205,34 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>58</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>59</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UMpx0zHjbYs</t>
+          <t>zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Why No One Respects You - The Daily Habits That Are Lowering Your VALUE</t>
+          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=UMpx0zHjbYs</t>
+          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1242,34 +1242,34 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>63</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dt_r6f3nLIQ</t>
+          <t>agifyuQrXW8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Why No One RESPECTS You — You Keep Making DISRESPECT Cheap</t>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Dt_r6f3nLIQ</t>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1279,34 +1279,34 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>224</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>b9Jj_A0dF4A</t>
+          <t>bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>If You React Like This, You Lose Respect Instantly</t>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=b9Jj_A0dF4A</t>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1316,34 +1316,34 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>194</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>41_ESKOfX-c</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>If You Don’t Respect Yourself, This Will Happen (Stoic Warning)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=41_ESKOfX-c</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1353,189 +1353,41 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>97</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>98</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>5,292</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>193</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TgBjzPpNOwA</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>brLELECTtR8</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>5,657</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>5,770</t>
+          <t>5,371</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,182 +465,182 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-21</t>
+          <t>Views_2026-04-22</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-22</t>
+          <t>Views_2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>ZervEMzTJp8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>The Second You Explain Your NO, It Stops Being One</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,059</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,076</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7V5HQ-od-c4</t>
+          <t>SnJkoHJPREc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why Your NO Starts Sounding Like a MAYBE</t>
+          <t>The Moment People Start Talking Over You</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
+          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>173</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>183</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hikgGDBJWiU</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2,076</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2,082</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ZJQ5tHebKPk</t>
+          <t>cv9HlXnQozI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Why TRYING TO BE UNDERSTOOD After DISRESPECT Makes You Lose POWER</t>
+          <t>The More You Let It Slide, The More They Push You</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZJQ5tHebKPk</t>
+          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>61</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>khBEVHIzKEM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>Why Being YOURSELF Is Keeping You STUCK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -650,34 +650,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,34 +687,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>340</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>344</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>khBEVHIzKEM</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Why Being YOURSELF Is Keeping You STUCK</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,34 +724,34 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>618</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>621</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C2ZZh6r6afI</t>
+          <t>Vye4llkNzwM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Moment Your Plans Start Sounding Empty</t>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -761,34 +761,34 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>68</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>cNyqLV3GFq8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>The More You Explain Your NO, The Less They Respect It</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -798,34 +798,34 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DRQBvtISgH8</t>
+          <t>hikgGDBJWiU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Public Humiliation Only Works If You React</t>
+          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
+          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -835,34 +835,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cv9HlXnQozI</t>
+          <t>C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The More You Let It Slide, The More They Push You</t>
+          <t>The Moment Your Plans Start Sounding Empty</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
+          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,34 +872,34 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SnJkoHJPREc</t>
+          <t>7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Moment People Start Talking Over You</t>
+          <t>Why Your NO Starts Sounding Like a MAYBE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -909,34 +909,34 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>uyK1jiL9Hek</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>Why One INSULT Can Ruin Your Entire Day</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=uyK1jiL9Hek</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -946,108 +946,108 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DZ0NL1qMM8A</t>
+          <t>ZJQ5tHebKPk</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The “JUST JOKING” Follow-Up Is the REAL Test</t>
+          <t>Why TRYING TO BE UNDERSTOOD After DISRESPECT Makes You Lose POWER</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DZ0NL1qMM8A</t>
+          <t>https://www.youtube.com/watch?v=ZJQ5tHebKPk</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cNyqLV3GFq8</t>
+          <t>Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The More You Explain Your NO, The Less They Respect It</t>
+          <t>How to Win People’s RESPECT Before You Say a Word</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
+          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fAEEc3xxmC8</t>
+          <t>DZ0NL1qMM8A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
+          <t>The “JUST JOKING” Follow-Up Is the REAL Test</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
+          <t>https://www.youtube.com/watch?v=DZ0NL1qMM8A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1057,34 +1057,34 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>UMpx0zHjbYs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>Why No One Respects You - The Daily Habits That Are Lowering Your VALUE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=UMpx0zHjbYs</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1094,34 +1094,34 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NV2qQaDdxDM</t>
+          <t>zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Every Time You KEEP THE PEACE After DISRESPECT, You Lose POWER</t>
+          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NV2qQaDdxDM</t>
+          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1131,34 +1131,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>64</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>65</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cxx0wy3mYzA</t>
+          <t>fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>How to Win People’s RESPECT Before You Say a Word</t>
+          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
+          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1168,34 +1168,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Um_JjU7jfPo</t>
+          <t>GO53yD8kmuY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
+          <t>13 Signs You're Being DISRESPECTED and Need to Take Action Now</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
+          <t>https://www.youtube.com/watch?v=GO53yD8kmuY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1205,34 +1205,34 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>121</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>zNiBsk4wAB4</t>
+          <t>-vU8JsRIpLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
+          <t>Disrespected? Use the 3-Second Stoic Rule (Marcus Aurelius)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
+          <t>https://www.youtube.com/watch?v=-vU8JsRIpLA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>98</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>99</t>
         </is>
       </c>
     </row>
@@ -1279,34 +1279,34 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>224</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>225</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1316,78 +1316,41 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>406</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>407</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>41_ESKOfX-c</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>If You Don’t Respect Yourself, This Will Happen (Stoic Warning)</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=41_ESKOfX-c</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>4,589</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>98</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>5,292</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>5,371</t>
+          <t>4,657</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -465,108 +465,108 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-22</t>
+          <t>Views_2026-04-23</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-23</t>
+          <t>Views_2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ZervEMzTJp8</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Second You Explain Your NO, It Stops Being One</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2,082</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2,092</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SnJkoHJPREc</t>
+          <t>ZervEMzTJp8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Moment People Start Talking Over You</t>
+          <t>The Second You Explain Your NO, It Stops Being One</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>aC9ORClv72g</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>Why the SECOND Ask Turns Your NO Into a MAYBE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,12 +576,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2,076</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2,082</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>67</t>
         </is>
       </c>
     </row>
@@ -645,39 +645,39 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>59</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,182 +687,182 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>407</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>411</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>669</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>673</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Vye4llkNzwM</t>
+          <t>uyK1jiL9Hek</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+          <t>Why One INSULT Can Ruin Your Entire Day</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+          <t>https://www.youtube.com/watch?v=uyK1jiL9Hek</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cNyqLV3GFq8</t>
+          <t>ZJQ5tHebKPk</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The More You Explain Your NO, The Less They Respect It</t>
+          <t>Why TRYING TO BE UNDERSTOOD After DISRESPECT Makes You Lose POWER</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
+          <t>https://www.youtube.com/watch?v=ZJQ5tHebKPk</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>58</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hikgGDBJWiU</t>
+          <t>zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
+          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
+          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C2ZZh6r6afI</t>
+          <t>7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Moment Your Plans Start Sounding Empty</t>
+          <t>Why Your NO Starts Sounding Like a MAYBE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
+          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,34 +872,34 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7V5HQ-od-c4</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Why Your NO Starts Sounding Like a MAYBE</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -909,34 +909,34 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>621</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>623</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>uyK1jiL9Hek</t>
+          <t>SnJkoHJPREc</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Why One INSULT Can Ruin Your Entire Day</t>
+          <t>The Moment People Start Talking Over You</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uyK1jiL9Hek</t>
+          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -946,34 +946,34 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>185</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ZJQ5tHebKPk</t>
+          <t>Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Why TRYING TO BE UNDERSTOOD After DISRESPECT Makes You Lose POWER</t>
+          <t>How to Win People’s RESPECT Before You Say a Word</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZJQ5tHebKPk</t>
+          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -983,34 +983,34 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>59</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cxx0wy3mYzA</t>
+          <t>DRQBvtISgH8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>How to Win People’s RESPECT Before You Say a Word</t>
+          <t>Public Humiliation Only Works If You React</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
+          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1020,108 +1020,108 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DZ0NL1qMM8A</t>
+          <t>Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The “JUST JOKING” Follow-Up Is the REAL Test</t>
+          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DZ0NL1qMM8A</t>
+          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>61</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UMpx0zHjbYs</t>
+          <t>bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Why No One Respects You - The Daily Habits That Are Lowering Your VALUE</t>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=UMpx0zHjbYs</t>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>194</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>196</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>zNiBsk4wAB4</t>
+          <t>WFY6UCmgi74</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
+          <t>Why Talking More Makes You Sound LESS Important</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
+          <t>https://www.youtube.com/watch?v=WFY6UCmgi74</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -1168,34 +1168,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GO53yD8kmuY</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13 Signs You're Being DISRESPECTED and Need to Take Action Now</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GO53yD8kmuY</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1205,34 +1205,34 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>232</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>-vU8JsRIpLA</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Disrespected? Use the 3-Second Stoic Rule (Marcus Aurelius)</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-vU8JsRIpLA</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1242,34 +1242,34 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>334</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>335</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>agifyuQrXW8</t>
+          <t>pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1279,34 +1279,34 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>112</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>113</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -1340,17 +1340,17 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>4,589</t>
+          <t>5,385</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4,657</t>
+          <t>5,455</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-23</t>
+          <t>Views_2026-04-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-24</t>
+          <t>Views_2026-04-26</t>
         </is>
       </c>
     </row>
@@ -497,224 +497,224 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,082</t>
+          <t>2,092</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,092</t>
+          <t>2,121</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ZervEMzTJp8</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Second You Explain Your NO, It Stops Being One</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>411</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>429</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>aC9ORClv72g</t>
+          <t>khBEVHIzKEM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Why the SECOND Ask Turns Your NO Into a MAYBE</t>
+          <t>Why Being YOURSELF Is Keeping You STUCK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
+          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cv9HlXnQozI</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The More You Let It Slide, The More They Push You</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>623</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>635</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>khBEVHIzKEM</t>
+          <t>aC9ORClv72g</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Why Being YOURSELF Is Keeping You STUCK</t>
+          <t>Why the SECOND Ask Turns Your NO Into a MAYBE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
+          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>hikgGDBJWiU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>DZ0NL1qMM8A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>The “JUST JOKING” Follow-Up Is the REAL Test</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=DZ0NL1qMM8A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,123 +724,123 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>uyK1jiL9Hek</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Why One INSULT Can Ruin Your Entire Day</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uyK1jiL9Hek</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>673</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>677</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ZJQ5tHebKPk</t>
+          <t>zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Why TRYING TO BE UNDERSTOOD After DISRESPECT Makes You Lose POWER</t>
+          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZJQ5tHebKPk</t>
+          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>68</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>72</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>zNiBsk4wAB4</t>
+          <t>DRQBvtISgH8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
+          <t>Public Humiliation Only Works If You React</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
+          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -867,113 +867,113 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>cv9HlXnQozI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>The More You Let It Slide, The More They Push You</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SnJkoHJPREc</t>
+          <t>Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Moment People Start Talking Over You</t>
+          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cxx0wy3mYzA</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>How to Win People’s RESPECT Before You Say a Word</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -983,34 +983,34 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>335</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>337</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DRQBvtISgH8</t>
+          <t>SnJkoHJPREc</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Public Humiliation Only Works If You React</t>
+          <t>The Moment People Start Talking Over You</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
+          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1020,34 +1020,34 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>187</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Um_JjU7jfPo</t>
+          <t>Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
+          <t>How to Win People’s RESPECT Before You Say a Word</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
+          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1069,22 +1069,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1094,34 +1094,34 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WFY6UCmgi74</t>
+          <t>C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Why Talking More Makes You Sound LESS Important</t>
+          <t>The Moment Your Plans Start Sounding Empty</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=WFY6UCmgi74</t>
+          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1131,34 +1131,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fAEEc3xxmC8</t>
+          <t>ZJQ5tHebKPk</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
+          <t>Why TRYING TO BE UNDERSTOOD After DISRESPECT Makes You Lose POWER</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
+          <t>https://www.youtube.com/watch?v=ZJQ5tHebKPk</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1168,34 +1168,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>58</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>59</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>uyK1jiL9Hek</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>Why One INSULT Can Ruin Your Entire Day</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=uyK1jiL9Hek</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1205,34 +1205,34 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>41_ESKOfX-c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>If You Don’t Respect Yourself, This Will Happen (Stoic Warning)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=41_ESKOfX-c</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1242,34 +1242,34 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>98</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>99</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pYH8XAZ8h0A</t>
+          <t>TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1279,34 +1279,34 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>77</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QvJhQNdR-iU</t>
+          <t>2OilqvW_HzY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
+          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
+          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>270</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>271</t>
         </is>
       </c>
     </row>
@@ -1340,17 +1340,17 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>127</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>5,385</t>
+          <t>5,302</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>5,455</t>
+          <t>5,429</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-24</t>
+          <t>Views_2026-04-26</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-26</t>
+          <t>Views_2026-04-28</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,092</t>
+          <t>2,121</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,121</t>
+          <t>2,149</t>
         </is>
       </c>
     </row>
@@ -534,197 +534,197 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>429</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>446</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>khBEVHIzKEM</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Why Being YOURSELF Is Keeping You STUCK</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>635</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>646</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>khBEVHIzKEM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>Why Being YOURSELF Is Keeping You STUCK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>74</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>aC9ORClv72g</t>
+          <t>hikgGDBJWiU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Why the SECOND Ask Turns Your NO Into a MAYBE</t>
+          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
+          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hikgGDBJWiU</t>
+          <t>SnJkoHJPREc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
+          <t>The Moment People Start Talking Over You</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
+          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>193</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DZ0NL1qMM8A</t>
+          <t>s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The “JUST JOKING” Follow-Up Is the REAL Test</t>
+          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DZ0NL1qMM8A</t>
+          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -756,39 +756,39 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>677</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>682</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>zNiBsk4wAB4</t>
+          <t>0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
+          <t>When You Speak Softly, People Start Ignoring You (Here’s Why)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
+          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -835,71 +835,71 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>39</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7V5HQ-od-c4</t>
+          <t>5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Why Your NO Starts Sounding Like a MAYBE</t>
+          <t>When They Try To Embarrass You, Do This</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
+          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cv9HlXnQozI</t>
+          <t>zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The More You Let It Slide, The More They Push You</t>
+          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
+          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>75</t>
         </is>
       </c>
     </row>
@@ -946,145 +946,145 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>64</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>344</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>347</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SnJkoHJPREc</t>
+          <t>cv9HlXnQozI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Moment People Start Talking Over You</t>
+          <t>The More You Let It Slide, The More They Push You</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>73</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cxx0wy3mYzA</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>How to Win People’s RESPECT Before You Say a Word</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>144</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>147</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fAEEc3xxmC8</t>
+          <t>2OilqvW_HzY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
+          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
+          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1094,71 +1094,71 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>271</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>273</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C2ZZh6r6afI</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Moment Your Plans Start Sounding Empty</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>337</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>339</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ZJQ5tHebKPk</t>
+          <t>7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Why TRYING TO BE UNDERSTOOD After DISRESPECT Makes You Lose POWER</t>
+          <t>Why Your NO Starts Sounding Like a MAYBE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZJQ5tHebKPk</t>
+          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1168,34 +1168,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>uyK1jiL9Hek</t>
+          <t>fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Why One INSULT Can Ruin Your Entire Day</t>
+          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uyK1jiL9Hek</t>
+          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1205,34 +1205,34 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>41_ESKOfX-c</t>
+          <t>C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>If You Don’t Respect Yourself, This Will Happen (Stoic Warning)</t>
+          <t>The Moment Your Plans Start Sounding Empty</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=41_ESKOfX-c</t>
+          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1242,34 +1242,34 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TgBjzPpNOwA</t>
+          <t>O-BjZNeGx94</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+          <t>The Moment You REACT Too Fast, You Lose CONTROL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+          <t>https://www.youtube.com/watch?v=O-BjZNeGx94</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1279,34 +1279,34 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2OilqvW_HzY</t>
+          <t>b9Jj_A0dF4A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+          <t>If You React Like This, You Lose Respect Instantly</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+          <t>https://www.youtube.com/watch?v=b9Jj_A0dF4A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1316,41 +1316,189 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>nvybbwOMwIA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>agifyuQrXW8</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>p_Z683xxqfs</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Always Available? That’s Why They Don’t Respect You (5 Stoic Rules)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=p_Z683xxqfs</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>5,302</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>5,429</t>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>6,234</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>6,363</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-26</t>
+          <t>Views_2026-04-28</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-28</t>
+          <t>Views_2026-04-29</t>
         </is>
       </c>
     </row>
@@ -497,113 +497,113 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,121</t>
+          <t>2,149</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,149</t>
+          <t>2,169</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>khBEVHIzKEM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>Why Being YOURSELF Is Keeping You STUCK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>82</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>446</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>454</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>khBEVHIzKEM</t>
+          <t>s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Why Being YOURSELF Is Keeping You STUCK</t>
+          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
+          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,71 +613,71 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hikgGDBJWiU</t>
+          <t>SnJkoHJPREc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
+          <t>The Moment People Start Talking Over You</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
+          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>199</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SnJkoHJPREc</t>
+          <t>hikgGDBJWiU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Moment People Start Talking Over You</t>
+          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,39 +687,39 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>39</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>s0GGaP5KHU4</t>
+          <t>RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
+          <t>When You WALK AWAY and They Say ONE MORE THING</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
+          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -729,66 +729,66 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>DRQBvtISgH8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>Public Humiliation Only Works If You React</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0a_DUuDQFx0</t>
+          <t>zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>When You Speak Softly, People Start Ignoring You (Here’s Why)</t>
+          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
+          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -798,34 +798,34 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DRQBvtISgH8</t>
+          <t>cv9HlXnQozI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Public Humiliation Only Works If You React</t>
+          <t>The More You Let It Slide, The More They Push You</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
+          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -835,34 +835,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>73</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5Ydh9Xglz9s</t>
+          <t>cNyqLV3GFq8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>When They Try To Embarrass You, Do This</t>
+          <t>The More You Explain Your NO, The Less They Respect It</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
+          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,71 +872,71 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>zNiBsk4wAB4</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>682</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>686</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Um_JjU7jfPo</t>
+          <t>b9Jj_A0dF4A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
+          <t>If You React Like This, You Lose Respect Instantly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
+          <t>https://www.youtube.com/watch?v=b9Jj_A0dF4A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -946,34 +946,34 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -983,34 +983,34 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>646</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>649</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cv9HlXnQozI</t>
+          <t>A0x6fkcrix4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The More You Let It Slide, The More They Push You</t>
+          <t>Never Defend Yourself Against Disrespect Here's Why</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
+          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1020,71 +1020,71 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>105</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>Vye4llkNzwM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>72</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2OilqvW_HzY</t>
+          <t>Dt_r6f3nLIQ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+          <t>Why No One RESPECTS You — You Keep Making DISRESPECT Cheap</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+          <t>https://www.youtube.com/watch?v=Dt_r6f3nLIQ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1094,34 +1094,34 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1131,108 +1131,108 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7V5HQ-od-c4</t>
+          <t>aC9ORClv72g</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Why Your NO Starts Sounding Like a MAYBE</t>
+          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
+          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fAEEc3xxmC8</t>
+          <t>UMpx0zHjbYs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
+          <t>Why No One Respects You - The Daily Habits That Are Lowering Your VALUE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
+          <t>https://www.youtube.com/watch?v=UMpx0zHjbYs</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>59</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C2ZZh6r6afI</t>
+          <t>7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Moment Your Plans Start Sounding Empty</t>
+          <t>Why Your NO Starts Sounding Like a MAYBE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
+          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1242,34 +1242,34 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>O-BjZNeGx94</t>
+          <t>C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Moment You REACT Too Fast, You Lose CONTROL</t>
+          <t>The Moment Your Plans Start Sounding Empty</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=O-BjZNeGx94</t>
+          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1279,34 +1279,34 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>b9Jj_A0dF4A</t>
+          <t>Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>If You React Like This, You Lose Respect Instantly</t>
+          <t>How to Win People’s RESPECT Before You Say a Word</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=b9Jj_A0dF4A</t>
+          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1316,34 +1316,34 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nvybbwOMwIA</t>
+          <t>QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
+          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
+          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1353,34 +1353,34 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>61</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>agifyuQrXW8</t>
+          <t>pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1390,34 +1390,34 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>114</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>p_Z683xxqfs</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Always Available? That’s Why They Don’t Respect You (5 Stoic Rules)</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=p_Z683xxqfs</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1427,34 +1427,34 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>233</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1464,41 +1464,152 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>347</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>348</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>agifyuQrXW8</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>nvybbwOMwIA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>6,234</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>6,363</t>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>6,109</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>6,223</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-28</t>
+          <t>Views_2026-04-29</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-29</t>
+          <t>Views_2026-04-30</t>
         </is>
       </c>
     </row>
@@ -497,54 +497,54 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,149</t>
+          <t>2,169</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,169</t>
+          <t>2,192</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>khBEVHIzKEM</t>
+          <t>RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why Being YOURSELF Is Keeping You STUCK</t>
+          <t>When You WALK AWAY and They Say ONE MORE THING</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
+          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -571,76 +571,76 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>454</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>464</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>s0GGaP5KHU4</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>649</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>656</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SnJkoHJPREc</t>
+          <t>khBEVHIzKEM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Moment People Start Talking Over You</t>
+          <t>Why Being YOURSELF Is Keeping You STUCK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -650,589 +650,589 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>100</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hikgGDBJWiU</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>686</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>689</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RQuIH8Wcqu0</t>
+          <t>hikgGDBJWiU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>When You WALK AWAY and They Say ONE MORE THING</t>
+          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
+          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DRQBvtISgH8</t>
+          <t>zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Public Humiliation Only Works If You React</t>
+          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
+          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>zNiBsk4wAB4</t>
+          <t>s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
+          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
+          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cv9HlXnQozI</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The More You Let It Slide, The More They Push You</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>348</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>350</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cNyqLV3GFq8</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The More You Explain Your NO, The Less They Respect It</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>235</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>SnJkoHJPREc</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>The Moment People Start Talking Over You</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>199</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>201</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>b9Jj_A0dF4A</t>
+          <t>GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>If You React Like This, You Lose Respect Instantly</t>
+          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=b9Jj_A0dF4A</t>
+          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>ZervEMzTJp8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>The Second You Explain Your NO, It Stops Being One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A0x6fkcrix4</t>
+          <t>0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Never Defend Yourself Against Disrespect Here's Why</t>
+          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
+          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Vye4llkNzwM</t>
+          <t>C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+          <t>The Moment Your Plans Start Sounding Empty</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dt_r6f3nLIQ</t>
+          <t>cv9HlXnQozI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Why No One RESPECTS You — You Keep Making DISRESPECT Cheap</t>
+          <t>The More You Let It Slide, The More They Push You</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Dt_r6f3nLIQ</t>
+          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>77</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Um_JjU7jfPo</t>
+          <t>QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
+          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
+          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>aC9ORClv72g</t>
+          <t>sGpvEkU4S-0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
+          <t>People Don’t Take You Seriously? Say These 5 Stoic Phrases | Stoic Lessons</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
+          <t>https://www.youtube.com/watch?v=sGpvEkU4S-0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>207</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>208</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UMpx0zHjbYs</t>
+          <t>nvybbwOMwIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Why No One Respects You - The Daily Habits That Are Lowering Your VALUE</t>
+          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=UMpx0zHjbYs</t>
+          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>69</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7V5HQ-od-c4</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Why Your NO Starts Sounding Like a MAYBE</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1242,374 +1242,41 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>339</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>340</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C2ZZh6r6afI</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Moment Your Plans Start Sounding Empty</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5,762</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Cxx0wy3mYzA</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>How to Win People’s RESPECT Before You Say a Word</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>QvJhQNdR-iU</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>pYH8XAZ8h0A</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>C19SUX9jC1o</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>9M1kjkk6oG8</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>agifyuQrXW8</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>nvybbwOMwIA</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>6,109</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>6,223</t>
+          <t>5,847</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-29</t>
+          <t>Views_2026-04-30</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-30</t>
+          <t>Views_2026-05-01</t>
         </is>
       </c>
     </row>
@@ -497,705 +497,705 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,169</t>
+          <t>2,192</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,192</t>
+          <t>2,214</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RQuIH8Wcqu0</t>
+          <t>khBEVHIzKEM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>When You WALK AWAY and They Say ONE MORE THING</t>
+          <t>Why Being YOURSELF Is Keeping You STUCK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
+          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>113</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>hikgGDBJWiU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>61</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>khBEVHIzKEM</t>
+          <t>RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Why Being YOURSELF Is Keeping You STUCK</t>
+          <t>When You WALK AWAY and They Say ONE MORE THING</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
+          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>DRQBvtISgH8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>Public Humiliation Only Works If You React</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>51</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hikgGDBJWiU</t>
+          <t>zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
+          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
+          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>81</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>zNiBsk4wAB4</t>
+          <t>b9Jj_A0dF4A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
+          <t>If You React Like This, You Lose Respect Instantly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
+          <t>https://www.youtube.com/watch?v=b9Jj_A0dF4A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>s0GGaP5KHU4</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>464</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>468</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>ZervEMzTJp8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>The Second You Explain Your NO, It Stops Being One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SnJkoHJPREc</t>
+          <t>DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Moment People Start Talking Over You</t>
+          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GJJ9OAXIZt8</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>689</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>691</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ZervEMzTJp8</t>
+          <t>UMpx0zHjbYs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Second You Explain Your NO, It Stops Being One</t>
+          <t>Why No One Respects You - The Daily Habits That Are Lowering Your VALUE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
+          <t>https://www.youtube.com/watch?v=UMpx0zHjbYs</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>61</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0a_DUuDQFx0</t>
+          <t>cv9HlXnQozI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
+          <t>The More You Let It Slide, The More They Push You</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
+          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>78</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C2ZZh6r6afI</t>
+          <t>SnJkoHJPREc</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Moment Your Plans Start Sounding Empty</t>
+          <t>The Moment People Start Talking Over You</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
+          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>201</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>203</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cv9HlXnQozI</t>
+          <t>7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The More You Let It Slide, The More They Push You</t>
+          <t>Why Your NO Starts Sounding Like a MAYBE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
+          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>QvJhQNdR-iU</t>
+          <t>A0x6fkcrix4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
+          <t>Never Defend Yourself Against Disrespect Here's Why</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
+          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>107</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sGpvEkU4S-0</t>
+          <t>Dt_r6f3nLIQ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>People Don’t Take You Seriously? Say These 5 Stoic Phrases | Stoic Lessons</t>
+          <t>Why No One RESPECTS You — You Keep Making DISRESPECT Cheap</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sGpvEkU4S-0</t>
+          <t>https://www.youtube.com/watch?v=Dt_r6f3nLIQ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>82</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>nvybbwOMwIA</t>
+          <t>DZ0NL1qMM8A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
+          <t>The “JUST JOKING” Follow-Up Is the REAL Test</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
+          <t>https://www.youtube.com/watch?v=DZ0NL1qMM8A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1205,34 +1205,34 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>cNyqLV3GFq8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>The More You Explain Your NO, The Less They Respect It</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1242,41 +1242,300 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Cxx0wy3mYzA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>How to Win People’s RESPECT Before You Say a Word</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>fAEEc3xxmC8</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Um_JjU7jfPo</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>agifyuQrXW8</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>p_Z683xxqfs</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Always Available? That’s Why They Don’t Respect You (5 Stoic Rules)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=p_Z683xxqfs</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>mpZoXoLMD3A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>5,762</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>5,847</t>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>5,615</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>5,727</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-04-30</t>
+          <t>Views_2026-05-01</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-01</t>
+          <t>Views_2026-05-02</t>
         </is>
       </c>
     </row>
@@ -497,335 +497,335 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,192</t>
+          <t>2,214</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,214</t>
+          <t>2,235</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>khBEVHIzKEM</t>
+          <t>z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why Being YOURSELF Is Keeping You STUCK</t>
+          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
+          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hikgGDBJWiU</t>
+          <t>SnJkoHJPREc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
+          <t>The Moment People Start Talking Over You</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
+          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>210</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GJJ9OAXIZt8</t>
+          <t>DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
+          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
+          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RQuIH8Wcqu0</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>When You WALK AWAY and They Say ONE MORE THING</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>691</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>697</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DRQBvtISgH8</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Public Humiliation Only Works If You React</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>657</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>662</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>zNiBsk4wAB4</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>468</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>473</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>b9Jj_A0dF4A</t>
+          <t>khBEVHIzKEM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>If You React Like This, You Lose Respect Instantly</t>
+          <t>Why Being YOURSELF Is Keeping You STUCK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=b9Jj_A0dF4A</t>
+          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>118</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>WFY6UCmgi74</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>Why Talking More Makes You Sound LESS Important</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=WFY6UCmgi74</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0a_DUuDQFx0</t>
+          <t>TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
+          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
+          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -835,108 +835,108 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>77</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ZervEMzTJp8</t>
+          <t>zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Second You Explain Your NO, It Stops Being One</t>
+          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
+          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DTMA3ZRpN08</t>
+          <t>agifyuQrXW8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>230</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>hikgGDBJWiU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -946,256 +946,256 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UMpx0zHjbYs</t>
+          <t>7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Why No One Respects You - The Daily Habits That Are Lowering Your VALUE</t>
+          <t>Why Your NO Starts Sounding Like a MAYBE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=UMpx0zHjbYs</t>
+          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cv9HlXnQozI</t>
+          <t>ZervEMzTJp8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The More You Let It Slide, The More They Push You</t>
+          <t>The Second You Explain Your NO, It Stops Being One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
+          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SnJkoHJPREc</t>
+          <t>RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Moment People Start Talking Over You</t>
+          <t>When You WALK AWAY and They Say ONE MORE THING</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7V5HQ-od-c4</t>
+          <t>NV2qQaDdxDM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Why Your NO Starts Sounding Like a MAYBE</t>
+          <t>Every Time You KEEP THE PEACE After DISRESPECT, You Lose POWER</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
+          <t>https://www.youtube.com/watch?v=NV2qQaDdxDM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A0x6fkcrix4</t>
+          <t>fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Never Defend Yourself Against Disrespect Here's Why</t>
+          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
+          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dt_r6f3nLIQ</t>
+          <t>DRQBvtISgH8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Why No One RESPECTS You — You Keep Making DISRESPECT Cheap</t>
+          <t>Public Humiliation Only Works If You React</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Dt_r6f3nLIQ</t>
+          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DZ0NL1qMM8A</t>
+          <t>cv9HlXnQozI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The “JUST JOKING” Follow-Up Is the REAL Test</t>
+          <t>The More You Let It Slide, The More They Push You</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DZ0NL1qMM8A</t>
+          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1205,12 +1205,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>81</t>
         </is>
       </c>
     </row>
@@ -1242,34 +1242,34 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cxx0wy3mYzA</t>
+          <t>g54e8p6ylts</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>How to Win People’s RESPECT Before You Say a Word</t>
+          <t>That “Quick Favor” Is Why They Disrespect You</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
+          <t>https://www.youtube.com/watch?v=g54e8p6ylts</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1279,34 +1279,34 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>fAEEc3xxmC8</t>
+          <t>Vye4llkNzwM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1316,34 +1316,34 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>72</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>73</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Um_JjU7jfPo</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1353,34 +1353,34 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>350</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>351</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>agifyuQrXW8</t>
+          <t>A0x6fkcrix4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+          <t>Never Defend Yourself Against Disrespect Here's Why</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1390,34 +1390,34 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>107</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>108</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1427,34 +1427,34 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>71</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>p_Z683xxqfs</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Always Available? That’s Why They Don’t Respect You (5 Stoic Rules)</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=p_Z683xxqfs</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1464,34 +1464,34 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>AB5Tw2Yd4qE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>When Your Point Gets Ignored, Don’t Repeat It—Say This (Stoic Rule)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=AB5Tw2Yd4qE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1501,41 +1501,374 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>IKtI1Kc9YC8</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>You’re Not Kind — You’re Being Used (5 Stoic Truths)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IKtI1Kc9YC8</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BypRuE0bqNg</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>If They Don’t Respect You, Walk Away (5 Seneca Rules)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BypRuE0bqNg</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1A1bXruIgD4</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Disrespected? These 10 Manipulative Phrases Make You Apologize (Stoic Replies)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1A1bXruIgD4</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TH331d5OGVs</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Disrespected in a Meeting? Do This (Stoic 30-Second Rule)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TH331d5OGVs</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>nSSLusuBoC8</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SET BOUNDARIES, GAIN RESPECT: 5 STOIC RULES (For People Who Get WALKED OVER)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nSSLusuBoC8</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>41_ESKOfX-c</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>If You Don’t Respect Yourself, This Will Happen (Stoic Warning)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=41_ESKOfX-c</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>FqpFUsYO-AQ</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>6 Reasons No One Takes You Seriously (Stoic Self-Respect Advice)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FqpFUsYO-AQ</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0w4OAOyEEUE</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>When They Interrupt You, Do This in 3 Seconds (Stoic)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0w4OAOyEEUE</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>5,615</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>5,727</t>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>6,916</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>7,020</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-01</t>
+          <t>Views_2026-05-02</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-02</t>
+          <t>Views_2026-05-03</t>
         </is>
       </c>
     </row>
@@ -497,44 +497,44 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,214</t>
+          <t>2,235</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,235</t>
+          <t>2,254</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>z1Qiw7QvFI0</t>
+          <t>8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
+          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
+          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -544,325 +544,325 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SnJkoHJPREc</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Moment People Start Talking Over You</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>473</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>482</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DTMA3ZRpN08</t>
+          <t>z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
+          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
+          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>697</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>700</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>Vye4llkNzwM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>73</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>khBEVHIzKEM</t>
+          <t>SnJkoHJPREc</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Why Being YOURSELF Is Keeping You STUCK</t>
+          <t>The Moment People Start Talking Over You</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
+          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>210</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>212</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WFY6UCmgi74</t>
+          <t>RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Why Talking More Makes You Sound LESS Important</t>
+          <t>When You WALK AWAY and They Say ONE MORE THING</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=WFY6UCmgi74</t>
+          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TgBjzPpNOwA</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>662</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>664</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>zNiBsk4wAB4</t>
+          <t>cv9HlXnQozI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
+          <t>The More You Let It Slide, The More They Push You</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
+          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,108 +872,108 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>81</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>83</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>agifyuQrXW8</t>
+          <t>s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hikgGDBJWiU</t>
+          <t>0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
+          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
+          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7V5HQ-od-c4</t>
+          <t>QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Why Your NO Starts Sounding Like a MAYBE</t>
+          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
+          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -983,34 +983,34 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>62</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ZervEMzTJp8</t>
+          <t>zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Second You Explain Your NO, It Stops Being One</t>
+          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
+          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1020,34 +1020,34 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>87</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>88</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RQuIH8Wcqu0</t>
+          <t>C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>When You WALK AWAY and They Say ONE MORE THING</t>
+          <t>The Moment Your Plans Start Sounding Empty</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
+          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1057,34 +1057,34 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NV2qQaDdxDM</t>
+          <t>WFY6UCmgi74</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Every Time You KEEP THE PEACE After DISRESPECT, You Lose POWER</t>
+          <t>Why Talking More Makes You Sound LESS Important</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NV2qQaDdxDM</t>
+          <t>https://www.youtube.com/watch?v=WFY6UCmgi74</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1094,34 +1094,34 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fAEEc3xxmC8</t>
+          <t>aC9ORClv72g</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
+          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
+          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1131,34 +1131,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DRQBvtISgH8</t>
+          <t>BypRuE0bqNg</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Public Humiliation Only Works If You React</t>
+          <t>If They Don’t Respect You, Walk Away (5 Seneca Rules)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
+          <t>https://www.youtube.com/watch?v=BypRuE0bqNg</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1168,34 +1168,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>74</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cv9HlXnQozI</t>
+          <t>5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The More You Let It Slide, The More They Push You</t>
+          <t>When They Try To Embarrass You, Do This</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
+          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1205,34 +1205,34 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cNyqLV3GFq8</t>
+          <t>g54e8p6ylts</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The More You Explain Your NO, The Less They Respect It</t>
+          <t>That “Quick Favor” Is Why They Disrespect You</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
+          <t>https://www.youtube.com/watch?v=g54e8p6ylts</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1242,633 +1242,41 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>g54e8p6ylts</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>That “Quick Favor” Is Why They Disrespect You</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=g54e8p6ylts</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>4,853</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Vye4llkNzwM</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>9M1kjkk6oG8</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A0x6fkcrix4</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Never Defend Yourself Against Disrespect Here's Why</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Um_JjU7jfPo</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>AB5Tw2Yd4qE</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>When Your Point Gets Ignored, Don’t Repeat It—Say This (Stoic Rule)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=AB5Tw2Yd4qE</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-01-04</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>IKtI1Kc9YC8</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>You’re Not Kind — You’re Being Used (5 Stoic Truths)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=IKtI1Kc9YC8</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>BypRuE0bqNg</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>If They Don’t Respect You, Walk Away (5 Seneca Rules)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=BypRuE0bqNg</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>1A1bXruIgD4</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Disrespected? These 10 Manipulative Phrases Make You Apologize (Stoic Replies)</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=1A1bXruIgD4</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2025-12-24</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>TH331d5OGVs</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Disrespected in a Meeting? Do This (Stoic 30-Second Rule)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=TH331d5OGVs</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2025-12-25</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>nSSLusuBoC8</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>SET BOUNDARIES, GAIN RESPECT: 5 STOIC RULES (For People Who Get WALKED OVER)</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=nSSLusuBoC8</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>41_ESKOfX-c</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>If You Don’t Respect Yourself, This Will Happen (Stoic Warning)</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=41_ESKOfX-c</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>FqpFUsYO-AQ</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>6 Reasons No One Takes You Seriously (Stoic Self-Respect Advice)</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=FqpFUsYO-AQ</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>0w4OAOyEEUE</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>When They Interrupt You, Do This in 3 Seconds (Stoic)</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=0w4OAOyEEUE</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>6,916</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>7,020</t>
+          <t>4,927</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-02</t>
+          <t>Views_2026-05-03</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-03</t>
+          <t>Views_2026-05-05</t>
         </is>
       </c>
     </row>
@@ -497,44 +497,44 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,235</t>
+          <t>2,254</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,254</t>
+          <t>2,325</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8fhVxgOWZ84</t>
+          <t>q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
+          <t>You OFFER First, So They Stop ASKING</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -571,520 +571,520 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>482</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>506</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>z1Qiw7QvFI0</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>664</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>679</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DTMA3ZRpN08</t>
+          <t>s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
+          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
+          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>agifyuQrXW8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>230</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>235</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vye4llkNzwM</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>700</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>705</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SnJkoHJPREc</t>
+          <t>hikgGDBJWiU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Moment People Start Talking Over You</t>
+          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>63</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RQuIH8Wcqu0</t>
+          <t>z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>When You WALK AWAY and They Say ONE MORE THING</t>
+          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
+          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cv9HlXnQozI</t>
+          <t>khBEVHIzKEM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The More You Let It Slide, The More They Push You</t>
+          <t>Why Being YOURSELF Is Keeping You STUCK</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
+          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>121</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>s0GGaP5KHU4</t>
+          <t>cNyqLV3GFq8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
+          <t>The More You Explain Your NO, The Less They Respect It</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
+          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0a_DUuDQFx0</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>351</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>354</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QvJhQNdR-iU</t>
+          <t>0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
+          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
+          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>zNiBsk4wAB4</t>
+          <t>7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
+          <t>Why Your NO Starts Sounding Like a MAYBE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
+          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C2ZZh6r6afI</t>
+          <t>nvybbwOMwIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Moment Your Plans Start Sounding Empty</t>
+          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
+          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>72</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WFY6UCmgi74</t>
+          <t>8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Why Talking More Makes You Sound LESS Important</t>
+          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=WFY6UCmgi74</t>
+          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -1131,34 +1131,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BypRuE0bqNg</t>
+          <t>fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>If They Don’t Respect You, Walk Away (5 Seneca Rules)</t>
+          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BypRuE0bqNg</t>
+          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1168,34 +1168,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5Ydh9Xglz9s</t>
+          <t>bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>When They Try To Embarrass You, Do This</t>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1205,34 +1205,34 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>199</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>g54e8p6ylts</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>That “Quick Favor” Is Why They Disrespect You</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=g54e8p6ylts</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1242,41 +1242,78 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>341</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>342</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>5IXlofJxEUg</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>When Someone Ignores You, Walk Away With Dignity (Stoic Guide)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5IXlofJxEUg</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>4,853</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>4,927</t>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>5,736</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>5,919</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-03</t>
+          <t>Views_2026-05-05</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-05</t>
+          <t>Views_2026-05-06</t>
         </is>
       </c>
     </row>
@@ -497,44 +497,44 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,254</t>
+          <t>2,325</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,325</t>
+          <t>2,351</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>q8sgDwcuE0A</t>
+          <t>lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>You OFFER First, So They Stop ASKING</t>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>506</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>511</t>
         </is>
       </c>
     </row>
@@ -608,224 +608,224 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>679</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>684</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>s0GGaP5KHU4</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>705</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>709</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>agifyuQrXW8</t>
+          <t>RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+          <t>When You WALK AWAY and They Say ONE MORE THING</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>You OFFER First, So They Stop ASKING</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hikgGDBJWiU</t>
+          <t>0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
+          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
+          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>z1Qiw7QvFI0</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>354</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>357</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DTMA3ZRpN08</t>
+          <t>Vye4llkNzwM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -835,34 +835,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>khBEVHIzKEM</t>
+          <t>hikgGDBJWiU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Why Being YOURSELF Is Keeping You STUCK</t>
+          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
+          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,108 +872,108 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cNyqLV3GFq8</t>
+          <t>ZervEMzTJp8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The More You Explain Your NO, The Less They Respect It</t>
+          <t>The Second You Explain Your NO, It Stops Being One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
+          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>qUd0X0Wn4-s</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>The Calm Response That Stops Rude People Fast</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>197</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0a_DUuDQFx0</t>
+          <t>7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
+          <t>Why Your NO Starts Sounding Like a MAYBE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
+          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -983,108 +983,108 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7V5HQ-od-c4</t>
+          <t>8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Why Your NO Starts Sounding Like a MAYBE</t>
+          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
+          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nvybbwOMwIA</t>
+          <t>SnJkoHJPREc</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
+          <t>The Moment People Start Talking Over You</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
+          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>212</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8fhVxgOWZ84</t>
+          <t>_qmVTMUQSDg</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
+          <t>10 STOIC PHRASES to SILENCE MANIPULATORS (Calm Boundaries)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
+          <t>https://www.youtube.com/watch?v=_qmVTMUQSDg</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1094,34 +1094,34 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>aC9ORClv72g</t>
+          <t>5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
+          <t>When They Try To Embarrass You, Do This</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
+          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1131,34 +1131,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fAEEc3xxmC8</t>
+          <t>nvybbwOMwIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
+          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
+          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1168,34 +1168,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>72</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>73</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1205,34 +1205,34 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>115</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>The Moment Your Plans Start Sounding Empty</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1242,34 +1242,34 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5IXlofJxEUg</t>
+          <t>2OilqvW_HzY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>When Someone Ignores You, Walk Away With Dignity (Stoic Guide)</t>
+          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5IXlofJxEUg</t>
+          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1279,41 +1279,115 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>274</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>TgBjzPpNOwA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>5,736</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>5,919</t>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>6,218</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>6,300</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-05</t>
+          <t>Views_2026-05-06</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-06</t>
+          <t>Views_2026-05-08</t>
         </is>
       </c>
     </row>
@@ -497,372 +497,372 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,325</t>
+          <t>2,351</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,351</t>
+          <t>2,391</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>lIx_B-vwa8g</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>511</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>528</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>3XX_s7f_zbk</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>When They Ask "Are You Sure?" — Do This</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>684</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>694</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RQuIH8Wcqu0</t>
+          <t>lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>When You WALK AWAY and They Say ONE MORE THING</t>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>q8sgDwcuE0A</t>
+          <t>0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>You OFFER First, So They Stop ASKING</t>
+          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
+          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0a_DUuDQFx0</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>709</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>714</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>hikgGDBJWiU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vye4llkNzwM</t>
+          <t>C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+          <t>The Moment Your Plans Start Sounding Empty</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hikgGDBJWiU</t>
+          <t>q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
+          <t>You OFFER First, So They Stop ASKING</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,108 +872,108 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ZervEMzTJp8</t>
+          <t>s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Second You Explain Your NO, It Stops Being One</t>
+          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
+          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>qUd0X0Wn4-s</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Calm Response That Stops Rude People Fast</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>343</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>346</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7V5HQ-od-c4</t>
+          <t>pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Why Your NO Starts Sounding Like a MAYBE</t>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -983,330 +983,330 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>115</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>117</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8fhVxgOWZ84</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>357</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>359</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SnJkoHJPREc</t>
+          <t>fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Moment People Start Talking Over You</t>
+          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>_qmVTMUQSDg</t>
+          <t>cv9HlXnQozI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10 STOIC PHRASES to SILENCE MANIPULATORS (Calm Boundaries)</t>
+          <t>The More You Let It Slide, The More They Push You</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_qmVTMUQSDg</t>
+          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5Ydh9Xglz9s</t>
+          <t>cNyqLV3GFq8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>When They Try To Embarrass You, Do This</t>
+          <t>The More You Explain Your NO, The Less They Respect It</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
+          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nvybbwOMwIA</t>
+          <t>RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
+          <t>When You WALK AWAY and They Say ONE MORE THING</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
+          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pYH8XAZ8h0A</t>
+          <t>qUd0X0Wn4-s</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+          <t>The Calm Response That Stops Rude People Fast</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>197</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>199</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C2ZZh6r6afI</t>
+          <t>_qmVTMUQSDg</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Moment Your Plans Start Sounding Empty</t>
+          <t>10 STOIC PHRASES to SILENCE MANIPULATORS (Calm Boundaries)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
+          <t>https://www.youtube.com/watch?v=_qmVTMUQSDg</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2OilqvW_HzY</t>
+          <t>QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>63</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>65</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TgBjzPpNOwA</t>
+          <t>7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+          <t>Why Your NO Starts Sounding Like a MAYBE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1316,34 +1316,34 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1353,41 +1353,448 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>8fhVxgOWZ84</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>aC9ORClv72g</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ZervEMzTJp8</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>The Second You Explain Your NO, It Stops Being One</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SnJkoHJPREc</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>The Moment People Start Talking Over You</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>WFY6UCmgi74</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Why Talking More Makes You Sound LESS Important</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WFY6UCmgi74</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AB5Tw2Yd4qE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>When Your Point Gets Ignored, Don’t Repeat It—Say This (Stoic Rule)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AB5Tw2Yd4qE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>nSSLusuBoC8</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SET BOUNDARIES, GAIN RESPECT: 5 STOIC RULES (For People Who Get WALKED OVER)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nSSLusuBoC8</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>wWnTzR023t8</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>How to Make People Respect You Without Chasing Anyone | Stoic Lessons</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wWnTzR023t8</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>agifyuQrXW8</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>B5ip0KwwVig</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>How To Command Respect As A Quiet Man | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=B5ip0KwwVig</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>6,218</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>6,300</t>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>6,670</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>6,834</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,293 +465,293 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-06</t>
+          <t>Views_2026-05-08</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-08</t>
+          <t>Views_2026-05-10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>The Moment You STOP, They Take Control</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,351</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,391</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3XX_s7f_zbk</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>When They Ask "Are You Sure?" — Do This</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2,391</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2,423</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>vBIa2dW5FJw</t>
+          <t>3XX_s7f_zbk</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>They Just Insulted You. You Said “Thank You.”</t>
+          <t>When They Ask "Are You Sure?" — Do This</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
+          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>lIx_B-vwa8g</t>
+          <t>0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
+          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
+          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0a_DUuDQFx0</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>714</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>720</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>When You WALK AWAY and They Say ONE MORE THING</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -761,71 +761,71 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hikgGDBJWiU</t>
+          <t>lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C2ZZh6r6afI</t>
+          <t>hikgGDBJWiU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Moment Your Plans Start Sounding Empty</t>
+          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
+          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -835,71 +835,71 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>q8sgDwcuE0A</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>You OFFER First, So They Stop ASKING</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>694</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>698</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>s0GGaP5KHU4</t>
+          <t>GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
+          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
+          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -909,71 +909,71 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pYH8XAZ8h0A</t>
+          <t>2Hqop6uU8PY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+          <t>“So Sensitive?” Here’s the Calm Stoic Response That Ends It</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+          <t>https://www.youtube.com/watch?v=2Hqop6uU8PY</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -983,34 +983,34 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1020,34 +1020,34 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fAEEc3xxmC8</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1057,256 +1057,256 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>528</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>530</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cv9HlXnQozI</t>
+          <t>DZ0NL1qMM8A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The More You Let It Slide, The More They Push You</t>
+          <t>The “JUST JOKING” Follow-Up Is the REAL Test</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
+          <t>https://www.youtube.com/watch?v=DZ0NL1qMM8A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cNyqLV3GFq8</t>
+          <t>fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The More You Explain Your NO, The Less They Respect It</t>
+          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
+          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RQuIH8Wcqu0</t>
+          <t>zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>When You WALK AWAY and They Say ONE MORE THING</t>
+          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
+          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>88</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>qUd0X0Wn4-s</t>
+          <t>WFY6UCmgi74</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Calm Response That Stops Rude People Fast</t>
+          <t>Why Talking More Makes You Sound LESS Important</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+          <t>https://www.youtube.com/watch?v=WFY6UCmgi74</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>_qmVTMUQSDg</t>
+          <t>7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10 STOIC PHRASES to SILENCE MANIPULATORS (Calm Boundaries)</t>
+          <t>Why Your NO Starts Sounding Like a MAYBE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_qmVTMUQSDg</t>
+          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>QvJhQNdR-iU</t>
+          <t>ZervEMzTJp8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
+          <t>The Second You Explain Your NO, It Stops Being One</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
+          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7V5HQ-od-c4</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Why Your NO Starts Sounding Like a MAYBE</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1316,34 +1316,34 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>236</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>z1Qiw7QvFI0</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1353,34 +1353,34 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>359</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>360</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8fhVxgOWZ84</t>
+          <t>QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
+          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
+          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1390,34 +1390,34 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>65</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>aC9ORClv72g</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1427,34 +1427,34 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ZervEMzTJp8</t>
+          <t>_qmVTMUQSDg</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Second You Explain Your NO, It Stops Being One</t>
+          <t>10 STOIC PHRASES to SILENCE MANIPULATORS (Calm Boundaries)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
+          <t>https://www.youtube.com/watch?v=_qmVTMUQSDg</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1464,34 +1464,34 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SnJkoHJPREc</t>
+          <t>Vye4llkNzwM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Moment People Start Talking Over You</t>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>WFY6UCmgi74</t>
+          <t>5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Why Talking More Makes You Sound LESS Important</t>
+          <t>When They Try To Embarrass You, Do This</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=WFY6UCmgi74</t>
+          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1538,34 +1538,34 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AB5Tw2Yd4qE</t>
+          <t>agifyuQrXW8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>When Your Point Gets Ignored, Don’t Repeat It—Say This (Stoic Rule)</t>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AB5Tw2Yd4qE</t>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1575,34 +1575,34 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>237</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>nSSLusuBoC8</t>
+          <t>2OilqvW_HzY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SET BOUNDARIES, GAIN RESPECT: 5 STOIC RULES (For People Who Get WALKED OVER)</t>
+          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nSSLusuBoC8</t>
+          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1612,34 +1612,34 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>274</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>275</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>wWnTzR023t8</t>
+          <t>0w4OAOyEEUE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>How to Make People Respect You Without Chasing Anyone | Stoic Lessons</t>
+          <t>When They Interrupt You, Do This in 3 Seconds (Stoic)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wWnTzR023t8</t>
+          <t>https://www.youtube.com/watch?v=0w4OAOyEEUE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1649,34 +1649,34 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>133</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>134</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>agifyuQrXW8</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1686,115 +1686,41 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>346</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>347</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>6,697</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>B5ip0KwwVig</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>How To Command Respect As A Quiet Man | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=B5ip0KwwVig</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>6,670</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>6,834</t>
+          <t>6,907</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-08</t>
+          <t>Views_2026-05-10</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-10</t>
+          <t>Views_2026-05-11</t>
         </is>
       </c>
     </row>
@@ -497,165 +497,165 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>58</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>vBIa2dW5FJw</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>They Just Insulted You. You Said “Thank You.”</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2,391</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2,423</t>
+          <t>58</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3XX_s7f_zbk</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>When They Ask "Are You Sure?" — Do This</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2,423</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>2,431</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>_FYXew5E_Xk</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>698</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>705</t>
         </is>
       </c>
     </row>
@@ -682,39 +682,39 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,86 +724,86 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RQuIH8Wcqu0</t>
+          <t>_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>When You WALK AWAY and They Say ONE MORE THING</t>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lIx_B-vwa8g</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>347</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>352</t>
         </is>
       </c>
     </row>
@@ -830,165 +830,165 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GJJ9OAXIZt8</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>530</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>535</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>s0GGaP5KHU4</t>
+          <t>q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
+          <t>You OFFER First, So They Stop ASKING</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2Hqop6uU8PY</t>
+          <t>3XX_s7f_zbk</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>“So Sensitive?” Here’s the Calm Stoic Response That Ends It</t>
+          <t>When They Ask "Are You Sure?" — Do This</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2Hqop6uU8PY</t>
+          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>45</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
     </row>
@@ -1020,34 +1020,34 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>When You WALK AWAY and They Say ONE MORE THING</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1057,108 +1057,108 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DZ0NL1qMM8A</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The “JUST JOKING” Follow-Up Is the REAL Test</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DZ0NL1qMM8A</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>360</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>362</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fAEEc3xxmC8</t>
+          <t>cNyqLV3GFq8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
+          <t>The More You Explain Your NO, The Less They Respect It</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
+          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>38</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>zNiBsk4wAB4</t>
+          <t>GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
+          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
+          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1168,34 +1168,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WFY6UCmgi74</t>
+          <t>ZervEMzTJp8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Why Talking More Makes You Sound LESS Important</t>
+          <t>The Second You Explain Your NO, It Stops Being One</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=WFY6UCmgi74</t>
+          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1205,34 +1205,34 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7V5HQ-od-c4</t>
+          <t>pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Why Your NO Starts Sounding Like a MAYBE</t>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1242,34 +1242,34 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>118</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ZervEMzTJp8</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Second You Explain Your NO, It Stops Being One</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1279,34 +1279,34 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>147</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>148</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>NV2qQaDdxDM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>Every Time You KEEP THE PEACE After DISRESPECT, You Lose POWER</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=NV2qQaDdxDM</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1316,34 +1316,34 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>SnJkoHJPREc</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>The Moment People Start Talking Over You</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1353,34 +1353,34 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>213</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>214</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>QvJhQNdR-iU</t>
+          <t>g54e8p6ylts</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
+          <t>That “Quick Favor” Is Why They Disrespect You</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
+          <t>https://www.youtube.com/watch?v=g54e8p6ylts</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1390,34 +1390,34 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>Vye4llkNzwM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1439,22 +1439,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>_qmVTMUQSDg</t>
+          <t>nvybbwOMwIA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10 STOIC PHRASES to SILENCE MANIPULATORS (Calm Boundaries)</t>
+          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_qmVTMUQSDg</t>
+          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1464,34 +1464,34 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>73</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Vye4llkNzwM</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1501,226 +1501,41 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>720</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>721</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5Ydh9Xglz9s</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>When They Try To Embarrass You, Do This</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>127</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>6,228</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>agifyuQrXW8</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2OilqvW_HzY</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>0w4OAOyEEUE</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>When They Interrupt You, Do This in 3 Seconds (Stoic)</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=0w4OAOyEEUE</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>346</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>6,697</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>6,907</t>
+          <t>6,355</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,86 +465,86 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-10</t>
+          <t>Views_2026-05-11</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-11</t>
+          <t>Views_2026-05-12</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bJKZPpJh1pI</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Moment You STOP, They Take Control</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2,431</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2,445</t>
         </is>
       </c>
     </row>
@@ -571,91 +571,91 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>58</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>The Moment You STOP, They Take Control</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2,423</t>
+          <t>58</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2,431</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -682,54 +682,54 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>s0GGaP5KHU4</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>705</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>709</t>
         </is>
       </c>
     </row>
@@ -756,409 +756,409 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>535</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>538</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hikgGDBJWiU</t>
+          <t>pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>121</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>lIx_B-vwa8g</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>238</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>202</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>q8sgDwcuE0A</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>You OFFER First, So They Stop ASKING</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>352</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>354</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3XX_s7f_zbk</t>
+          <t>DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>When They Ask "Are You Sure?" — Do This</t>
+          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
+          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DTMA3ZRpN08</t>
+          <t>8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
+          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
+          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RQuIH8Wcqu0</t>
+          <t>z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>When You WALK AWAY and They Say ONE MORE THING</t>
+          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
+          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>The Moment Your Plans Start Sounding Empty</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cNyqLV3GFq8</t>
+          <t>cv9HlXnQozI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The More You Explain Your NO, The Less They Respect It</t>
+          <t>The More You Let It Slide, The More They Push You</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
+          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>86</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GJJ9OAXIZt8</t>
+          <t>RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
+          <t>When You WALK AWAY and They Say ONE MORE THING</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
+          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1168,34 +1168,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ZervEMzTJp8</t>
+          <t>aC9ORClv72g</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Second You Explain Your NO, It Stops Being One</t>
+          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
+          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1205,34 +1205,34 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pYH8XAZ8h0A</t>
+          <t>GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1242,34 +1242,34 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>2Hqop6uU8PY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>“So Sensitive?” Here’s the Calm Stoic Response That Ends It</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=2Hqop6uU8PY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1279,34 +1279,34 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NV2qQaDdxDM</t>
+          <t>5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Every Time You KEEP THE PEACE After DISRESPECT, You Lose POWER</t>
+          <t>When They Try To Embarrass You, Do This</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NV2qQaDdxDM</t>
+          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1316,34 +1316,34 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SnJkoHJPREc</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Moment People Start Talking Over You</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1353,189 +1353,41 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>721</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>722</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>g54e8p6ylts</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>That “Quick Favor” Is Why They Disrespect You</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=g54e8p6ylts</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>5,843</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Vye4llkNzwM</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>nvybbwOMwIA</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>721</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>6,228</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>6,355</t>
+          <t>5,921</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,123 +465,123 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-11</t>
+          <t>Views_2026-05-12</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-12</t>
+          <t>Views_2026-05-13</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2,445</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>2,456</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2,431</t>
+          <t>709</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2,445</t>
+          <t>718</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>vBIa2dW5FJw</t>
+          <t>lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>They Just Insulted You. You Said “Thank You.”</t>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -613,71 +613,71 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>63</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>lIx_B-vwa8g</t>
+          <t>RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
+          <t>When You WALK AWAY and They Say ONE MORE THING</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
+          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0a_DUuDQFx0</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,34 +687,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>81</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,108 +724,108 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>366</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>_FYXew5E_Xk</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>538</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>542</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pYH8XAZ8h0A</t>
+          <t>nvybbwOMwIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -835,340 +835,340 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>74</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>Vye4llkNzwM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>81</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>3XX_s7f_zbk</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+          <t>When They Ask "Are You Sure?" — Do This</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>241</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DTMA3ZRpN08</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>722</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>725</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8fhVxgOWZ84</t>
+          <t>wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
+          <t>The Moment You REACT, They Know Where To Press</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
+          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>z1Qiw7QvFI0</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C2ZZh6r6afI</t>
+          <t>q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Moment Your Plans Start Sounding Empty</t>
+          <t>You OFFER First, So They Stop ASKING</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cv9HlXnQozI</t>
+          <t>s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The More You Let It Slide, The More They Push You</t>
+          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
+          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RQuIH8Wcqu0</t>
+          <t>0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>When You WALK AWAY and They Say ONE MORE THING</t>
+          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
+          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1200,194 +1200,675 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GJJ9OAXIZt8</t>
+          <t>z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
+          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
+          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2Hqop6uU8PY</t>
+          <t>41_ESKOfX-c</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>“So Sensitive?” Here’s the Calm Stoic Response That Ends It</t>
+          <t>If You Don’t Respect Yourself, This Will Happen (Stoic Warning)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2Hqop6uU8PY</t>
+          <t>https://www.youtube.com/watch?v=41_ESKOfX-c</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>102</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5Ydh9Xglz9s</t>
+          <t>bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>When They Try To Embarrass You, Do This</t>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>202</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>204</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>354</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>356</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>SnJkoHJPREc</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>The Moment People Start Talking Over You</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>C2ZZh6r6afI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>The Moment Your Plans Start Sounding Empty</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cv9HlXnQozI</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>The More You Let It Slide, The More They Push You</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DTMA3ZRpN08</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>8fhVxgOWZ84</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>pYH8XAZ8h0A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A0x6fkcrix4</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Never Defend Yourself Against Disrespect Here's Why</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>khBEVHIzKEM</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Why Being YOURSELF Is Keeping You STUCK</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>QvJhQNdR-iU</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AB5Tw2Yd4qE</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>When Your Point Gets Ignored, Don’t Repeat It—Say This (Stoic Rule)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AB5Tw2Yd4qE</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>_qmVTMUQSDg</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>10 STOIC PHRASES to SILENCE MANIPULATORS (Calm Boundaries)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_qmVTMUQSDg</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>qUd0X0Wn4-s</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>The Calm Response That Stops Rude People Fast</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>nSSLusuBoC8</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SET BOUNDARIES, GAIN RESPECT: 5 STOIC RULES (For People Who Get WALKED OVER)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nSSLusuBoC8</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>5,843</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>5,921</t>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>7,354</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>7,454</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-12</t>
+          <t>Views_2026-05-13</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-13</t>
+          <t>Views_2026-05-15</t>
         </is>
       </c>
     </row>
@@ -497,461 +497,461 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,445</t>
+          <t>2,456</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,456</t>
+          <t>2,488</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>56</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>lIx_B-vwa8g</t>
+          <t>vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>63</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bJKZPpJh1pI</t>
+          <t>lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Moment You STOP, They Take Control</t>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RQuIH8Wcqu0</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>When You WALK AWAY and They Say ONE MORE THING</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>718</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>731</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>3XX_s7f_zbk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>When They Ask "Are You Sure?" — Do This</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>542</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>551</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>When You WALK AWAY and They Say ONE MORE THING</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GJJ9OAXIZt8</t>
+          <t>_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nvybbwOMwIA</t>
+          <t>GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
+          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
+          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Vye4llkNzwM</t>
+          <t>8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3XX_s7f_zbk</t>
+          <t>wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>When They Ask "Are You Sure?" — Do This</t>
+          <t>The Moment You REACT, They Know Where To Press</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
+          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -978,261 +978,261 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>725</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>732</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>wus2BJY5Gtk</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Moment You REACT, They Know Where To Press</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>356</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>362</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>hzoRggV72as</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>They Ignore You Because You Still Let Them Back IN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>q8sgDwcuE0A</t>
+          <t>s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>You OFFER First, So They Stop ASKING</t>
+          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
+          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>s0GGaP5KHU4</t>
+          <t>z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
+          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
+          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0a_DUuDQFx0</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>aC9ORClv72g</t>
+          <t>q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
+          <t>You OFFER First, So They Stop ASKING</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>z1Qiw7QvFI0</t>
+          <t>qtid1KrxsOg</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
+          <t>The Real Mistake After DISRESPECT Is Trying to PROVE Yourself</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
+          <t>https://www.youtube.com/watch?v=qtid1KrxsOg</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1242,34 +1242,34 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>41_ESKOfX-c</t>
+          <t>hikgGDBJWiU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>If You Don’t Respect Yourself, This Will Happen (Stoic Warning)</t>
+          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=41_ESKOfX-c</t>
+          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1279,34 +1279,34 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>86</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+          <t>The Moment You STOP, They Take Control</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1316,34 +1316,34 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>68</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1353,330 +1353,330 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SnJkoHJPREc</t>
+          <t>ZervEMzTJp8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Moment People Start Talking Over You</t>
+          <t>The Second You Explain Your NO, It Stops Being One</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C2ZZh6r6afI</t>
+          <t>TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Moment Your Plans Start Sounding Empty</t>
+          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
+          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>78</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cv9HlXnQozI</t>
+          <t>_qmVTMUQSDg</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The More You Let It Slide, The More They Push You</t>
+          <t>10 STOIC PHRASES to SILENCE MANIPULATORS (Calm Boundaries)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
+          <t>https://www.youtube.com/watch?v=_qmVTMUQSDg</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DTMA3ZRpN08</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>148</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>150</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8fhVxgOWZ84</t>
+          <t>41_ESKOfX-c</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
+          <t>If You Don’t Respect Yourself, This Will Happen (Stoic Warning)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
+          <t>https://www.youtube.com/watch?v=41_ESKOfX-c</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>104</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pYH8XAZ8h0A</t>
+          <t>Vye4llkNzwM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>86</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A0x6fkcrix4</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Never Defend Yourself Against Disrespect Here's Why</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>366</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>368</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>khBEVHIzKEM</t>
+          <t>8yCYD0b2zsM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Why Being YOURSELF Is Keeping You STUCK</t>
+          <t>Why EXPLAINING After DISRESPECT Makes You Look Weaker</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
+          <t>https://www.youtube.com/watch?v=8yCYD0b2zsM</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>56</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QvJhQNdR-iU</t>
+          <t>cNyqLV3GFq8</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
+          <t>The More You Explain Your NO, The Less They Respect It</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
+          <t>https://www.youtube.com/watch?v=cNyqLV3GFq8</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1686,34 +1686,34 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AB5Tw2Yd4qE</t>
+          <t>NV2qQaDdxDM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>When Your Point Gets Ignored, Don’t Repeat It—Say This (Stoic Rule)</t>
+          <t>Every Time You KEEP THE PEACE After DISRESPECT, You Lose POWER</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AB5Tw2Yd4qE</t>
+          <t>https://www.youtube.com/watch?v=NV2qQaDdxDM</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1723,34 +1723,34 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>_qmVTMUQSDg</t>
+          <t>ZJQ5tHebKPk</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10 STOIC PHRASES to SILENCE MANIPULATORS (Calm Boundaries)</t>
+          <t>Why TRYING TO BE UNDERSTOOD After DISRESPECT Makes You Lose POWER</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_qmVTMUQSDg</t>
+          <t>https://www.youtube.com/watch?v=ZJQ5tHebKPk</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1760,34 +1760,34 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>qUd0X0Wn4-s</t>
+          <t>Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Calm Response That Stops Rude People Fast</t>
+          <t>How to Win People’s RESPECT Before You Say a Word</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1797,34 +1797,34 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>63</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>nSSLusuBoC8</t>
+          <t>Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SET BOUNDARIES, GAIN RESPECT: 5 STOIC RULES (For People Who Get WALKED OVER)</t>
+          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nSSLusuBoC8</t>
+          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1834,41 +1834,781 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>71</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>fAEEc3xxmC8</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>zNiBsk4wAB4</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Why DISRESPECT Keeps Repeating When You Stay QUIET</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zNiBsk4wAB4</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>wFR_Ps8sLlI</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Never Lose Control When Someone Disrespects You</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wFR_Ps8sLlI</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>nvybbwOMwIA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BypRuE0bqNg</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>If They Don’t Respect You, Walk Away (5 Seneca Rules)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BypRuE0bqNg</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TH331d5OGVs</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Disrespected in a Meeting? Do This (Stoic 30-Second Rule)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TH331d5OGVs</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AB5Tw2Yd4qE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>When Your Point Gets Ignored, Don’t Repeat It—Say This (Stoic Rule)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AB5Tw2Yd4qE</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>5Ydh9Xglz9s</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>When They Try To Embarrass You, Do This</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>O-BjZNeGx94</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>The Moment You REACT Too Fast, You Lose CONTROL</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=O-BjZNeGx94</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>-vU8JsRIpLA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Disrespected? Use the 3-Second Stoic Rule (Marcus Aurelius)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-vU8JsRIpLA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>5IXlofJxEUg</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>When Someone Ignores You, Walk Away With Dignity (Stoic Guide)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5IXlofJxEUg</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0w4OAOyEEUE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>When They Interrupt You, Do This in 3 Seconds (Stoic)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0w4OAOyEEUE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>wWnTzR023t8</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>How to Make People Respect You Without Chasing Anyone | Stoic Lessons</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wWnTzR023t8</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2OilqvW_HzY</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>_yE_ZMKH03Y</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Stop Overreacting When People Disrespect You – 7 Stoic Rules to Keep Your Calm | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_yE_ZMKH03Y</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>p_Z683xxqfs</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Always Available? That’s Why They Don’t Respect You (5 Stoic Rules)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=p_Z683xxqfs</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>qUd0X0Wn4-s</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>The Calm Response That Stops Rude People Fast</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>B5ip0KwwVig</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>How To Command Respect As A Quiet Man | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=B5ip0KwwVig</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>fMZNVUsnWlw</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Low Self-Worth: 3 Stoic Rules To Rebuild Your Inner Value</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fMZNVUsnWlw</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>7,354</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>7,454</t>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>8,562</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>8,805</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,123 +465,123 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-15</t>
+          <t>Views_2026-05-16</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-16</t>
+          <t>Views_2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>The Moment You STOP, They Take Control</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,488</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,510</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>2,510</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>2,521</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hzoRggV72as</t>
+          <t>_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>They Ignore You Because You Still Let Them Back IN</t>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -608,261 +608,261 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>73</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kRwhF5oBg5w</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>They Don’t Need Your Reasons — They Need Your WEAK SPOT</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kRwhF5oBg5w</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>745</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>750</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>vBIa2dW5FJw</t>
+          <t>kRwhF5oBg5w</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>They Just Insulted You. You Said “Thank You.”</t>
+          <t>They Don’t Need Your Reasons — They Need Your WEAK SPOT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
+          <t>https://www.youtube.com/watch?v=kRwhF5oBg5w</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>_FYXew5E_Xk</t>
+          <t>z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
+          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
+          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>hzoRggV72as</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>They Ignore You Because You Still Let Them Back IN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>q8sgDwcuE0A</t>
+          <t>lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>You OFFER First, So They Stop ASKING</t>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>53</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>88</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0a_DUuDQFx0</t>
+          <t>q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
+          <t>You OFFER First, So They Stop ASKING</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,34 +872,34 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5Ydh9Xglz9s</t>
+          <t>GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>When They Try To Embarrass You, Do This</t>
+          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
+          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -909,34 +909,34 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>3XX_s7f_zbk</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>When They Ask "Are You Sure?" — Do This</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -946,108 +946,108 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>wus2BJY5Gtk</t>
+          <t>08eQH53fdLY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Moment You REACT, They Know Where To Press</t>
+          <t>When You Move FIRST, They Stop Planning Ahead</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
+          <t>https://www.youtube.com/watch?v=08eQH53fdLY</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DTMA3ZRpN08</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>555</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>558</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3XX_s7f_zbk</t>
+          <t>41_ESKOfX-c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>When They Ask "Are You Sure?" — Do This</t>
+          <t>If You Don’t Respect Yourself, This Will Happen (Stoic Warning)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
+          <t>https://www.youtube.com/watch?v=41_ESKOfX-c</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1057,34 +1057,34 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>106</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>agifyuQrXW8</t>
+          <t>wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+          <t>The Moment You REACT, They Know Where To Press</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1094,34 +1094,34 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pYH8XAZ8h0A</t>
+          <t>DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1131,256 +1131,256 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>s0GGaP5KHU4</t>
+          <t>bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>205</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>207</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RQuIH8Wcqu0</t>
+          <t>0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>When You WALK AWAY and They Say ONE MORE THING</t>
+          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
+          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>55</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>56</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>ZervEMzTJp8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>The Second You Explain Your NO, It Stops Being One</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Um_JjU7jfPo</t>
+          <t>agifyuQrXW8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>241</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7V5HQ-od-c4</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Why Your NO Starts Sounding Like a MAYBE</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7V5HQ-od-c4</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>738</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>740</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hikgGDBJWiU</t>
+          <t>UnPmWxqA9Vw</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
+          <t>This Question Is a Trap: 5 Stoic Rules for Dealing With Manipulators | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
+          <t>https://www.youtube.com/watch?v=UnPmWxqA9Vw</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>313</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>315</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DZ0NL1qMM8A</t>
+          <t>8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The “JUST JOKING” Follow-Up Is the REAL Test</t>
+          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DZ0NL1qMM8A</t>
+          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1390,34 +1390,34 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ZervEMzTJp8</t>
+          <t>wWnTzR023t8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Second You Explain Your NO, It Stops Being One</t>
+          <t>How to Make People Respect You Without Chasing Anyone | Stoic Lessons</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
+          <t>https://www.youtube.com/watch?v=wWnTzR023t8</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1427,34 +1427,34 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>64</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>65</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5IXlofJxEUg</t>
+          <t>RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>When Someone Ignores You, Walk Away With Dignity (Stoic Guide)</t>
+          <t>When You WALK AWAY and They Say ONE MORE THING</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5IXlofJxEUg</t>
+          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1464,34 +1464,34 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Vye4llkNzwM</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1501,41 +1501,115 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>365</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>366</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Vye4llkNzwM</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>QvJhQNdR-iU</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>6,490</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>6,618</t>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>6,686</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>6,788</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-16</t>
+          <t>Views_2026-05-17</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-17</t>
+          <t>Views_2026-05-18</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2,510</t>
+          <t>2,521</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2,521</t>
+          <t>2,533</t>
         </is>
       </c>
     </row>
@@ -571,113 +571,113 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>59</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>91</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>98</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>You Called It MINOR. They Called It PERMISSION.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kRwhF5oBg5w</t>
+          <t>z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>They Don’t Need Your Reasons — They Need Your WEAK SPOT</t>
+          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kRwhF5oBg5w</t>
+          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,34 +687,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>z1Qiw7QvFI0</t>
+          <t>8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
+          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
+          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,145 +724,145 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hzoRggV72as</t>
+          <t>q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>They Ignore You Because You Still Let Them Back IN</t>
+          <t>You OFFER First, So They Stop ASKING</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>46</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lIx_B-vwa8g</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>73</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>vBIa2dW5FJw</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>They Just Insulted You. You Said “Thank You.”</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>245</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>q8sgDwcuE0A</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>You OFFER First, So They Stop ASKING</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,34 +872,34 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>558</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>561</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GJJ9OAXIZt8</t>
+          <t>lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -946,34 +946,34 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08eQH53fdLY</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>When You Move FIRST, They Stop Planning Ahead</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=08eQH53fdLY</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -983,34 +983,34 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>740</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>743</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1020,71 +1020,71 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>41_ESKOfX-c</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>If You Don’t Respect Yourself, This Will Happen (Stoic Warning)</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=41_ESKOfX-c</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>750</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>753</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>wus2BJY5Gtk</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Moment You REACT, They Know Where To Press</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1094,34 +1094,34 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>152</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DTMA3ZRpN08</t>
+          <t>pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1131,34 +1131,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>124</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>126</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1168,34 +1168,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0a_DUuDQFx0</t>
+          <t>aC9ORClv72g</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
+          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
+          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1205,182 +1205,182 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ZervEMzTJp8</t>
+          <t>08eQH53fdLY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Second You Explain Your NO, It Stops Being One</t>
+          <t>When You Move FIRST, They Stop Planning Ahead</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
+          <t>https://www.youtube.com/watch?v=08eQH53fdLY</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>agifyuQrXW8</t>
+          <t>kRwhF5oBg5w</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+          <t>They Don’t Need Your Reasons — They Need Your WEAK SPOT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+          <t>https://www.youtube.com/watch?v=kRwhF5oBg5w</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UnPmWxqA9Vw</t>
+          <t>C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>This Question Is a Trap: 5 Stoic Rules for Dealing With Manipulators | Stoic Wisdom</t>
+          <t>The Moment Your Plans Start Sounding Empty</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=UnPmWxqA9Vw</t>
+          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8fhVxgOWZ84</t>
+          <t>QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
+          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
+          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1390,226 +1390,41 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>68</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>wWnTzR023t8</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>How to Make People Respect You Without Chasing Anyone | Stoic Lessons</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=wWnTzR023t8</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>5,823</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>RQuIH8Wcqu0</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>When You WALK AWAY and They Say ONE MORE THING</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Vye4llkNzwM</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>QvJhQNdR-iU</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>6,686</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>6,788</t>
+          <t>5,926</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-17</t>
+          <t>Views_2026-05-18</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-18</t>
+          <t>Views_2026-05-19</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>128</t>
         </is>
       </c>
     </row>
@@ -539,71 +539,71 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2,521</t>
+          <t>2,533</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2,533</t>
+          <t>2,545</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>_FYXew5E_Xk</t>
+          <t>lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>vBIa2dW5FJw</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>They Just Insulted You. You Said “Thank You.”</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,123 +613,123 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>561</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>568</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You Called It MINOR. They Called It PERMISSION.</t>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>98</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>105</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>z1Qiw7QvFI0</t>
+          <t>_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>65</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8fhVxgOWZ84</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>753</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>759</t>
         </is>
       </c>
     </row>
@@ -756,76 +756,76 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>56</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>743</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>748</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>3XX_s7f_zbk</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>When They Ask "Are You Sure?" — Do This</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -835,34 +835,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>63</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>LYoP33V12SU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>Your REACTION Became Their Evidence</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=LYoP33V12SU</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,34 +872,34 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>lIx_B-vwa8g</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -909,34 +909,34 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>77</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3XX_s7f_zbk</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>When They Ask "Are You Sure?" — Do This</t>
+          <t>You Called It MINOR. They Called It PERMISSION.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -946,145 +946,145 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>89</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DTMA3ZRpN08</t>
+          <t>agifyuQrXW8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>243</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>The Moment You REACT, They Know Where To Press</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1094,145 +1094,145 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pYH8XAZ8h0A</t>
+          <t>z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GJJ9OAXIZt8</t>
+          <t>kRwhF5oBg5w</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
+          <t>They Don’t Need Your Reasons — They Need Your WEAK SPOT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
+          <t>https://www.youtube.com/watch?v=kRwhF5oBg5w</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>aC9ORClv72g</t>
+          <t>DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
+          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
+          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08eQH53fdLY</t>
+          <t>GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>When You Move FIRST, They Stop Planning Ahead</t>
+          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=08eQH53fdLY</t>
+          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1242,34 +1242,34 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kRwhF5oBg5w</t>
+          <t>Vye4llkNzwM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>They Don’t Need Your Reasons — They Need Your WEAK SPOT</t>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kRwhF5oBg5w</t>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1279,34 +1279,34 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>88</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>s0GGaP5KHU4</t>
+          <t>5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
+          <t>When They Try To Embarrass You, Do This</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
+          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1316,34 +1316,34 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C2ZZh6r6afI</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Moment Your Plans Start Sounding Empty</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1353,34 +1353,34 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>246</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>QvJhQNdR-iU</t>
+          <t>wFR_Ps8sLlI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
+          <t>Never Lose Control When Someone Disrespects You</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
+          <t>https://www.youtube.com/watch?v=wFR_Ps8sLlI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1390,41 +1390,189 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>66</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>C2ZZh6r6afI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>The Moment Your Plans Start Sounding Empty</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>aC9ORClv72g</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TgBjzPpNOwA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>5,823</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>5,926</t>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>6,527</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>6,645</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-18</t>
+          <t>Views_2026-05-19</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-19</t>
+          <t>Views_2026-05-21</t>
         </is>
       </c>
     </row>
@@ -497,54 +497,54 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>128</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>150</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2,533</t>
+          <t>759</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2,545</t>
+          <t>776</t>
         </is>
       </c>
     </row>
@@ -571,91 +571,91 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>64</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>2,545</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>2,559</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>vBIa2dW5FJw</t>
+          <t>kRwhF5oBg5w</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>They Just Insulted You. You Said “Thank You.”</t>
+          <t>They Don’t Need Your Reasons — They Need Your WEAK SPOT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
+          <t>https://www.youtube.com/watch?v=kRwhF5oBg5w</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -682,39 +682,39 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,34 +724,34 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>86</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>q8sgDwcuE0A</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>You OFFER First, So They Stop ASKING</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -761,409 +761,409 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>91</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>568</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>574</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3XX_s7f_zbk</t>
+          <t>08eQH53fdLY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>When They Ask "Are You Sure?" — Do This</t>
+          <t>When You Move FIRST, They Stop Planning Ahead</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
+          <t>https://www.youtube.com/watch?v=08eQH53fdLY</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LYoP33V12SU</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Your REACTION Became Their Evidence</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=LYoP33V12SU</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>748</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>754</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>367</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>372</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>You Called It MINOR. They Called It PERMISSION.</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>250</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>You OFFER First, So They Stop ASKING</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>agifyuQrXW8</t>
+          <t>vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>109</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>wus2BJY5Gtk</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Moment You REACT, They Know Where To Press</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>369</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>373</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8fhVxgOWZ84</t>
+          <t>hzoRggV72as</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
+          <t>They Ignore You Because You Still Let Them Back IN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
+          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>z1Qiw7QvFI0</t>
+          <t>3XX_s7f_zbk</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
+          <t>When They Ask "Are You Sure?" — Do This</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
+          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kRwhF5oBg5w</t>
+          <t>wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>They Don’t Need Your Reasons — They Need Your WEAK SPOT</t>
+          <t>The Moment You REACT, They Know Where To Press</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kRwhF5oBg5w</t>
+          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1173,214 +1173,214 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DTMA3ZRpN08</t>
+          <t>s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
+          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
+          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GJJ9OAXIZt8</t>
+          <t>z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
+          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
+          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>39</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Vye4llkNzwM</t>
+          <t>LYoP33V12SU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+          <t>Your REACTION Became Their Evidence</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+          <t>https://www.youtube.com/watch?v=LYoP33V12SU</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5Ydh9Xglz9s</t>
+          <t>8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>When They Try To Embarrass You, Do This</t>
+          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
+          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>126</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>128</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>wFR_Ps8sLlI</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Never Lose Control When Someone Disrespects You</t>
+          <t>You Called It MINOR. They Called It PERMISSION.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wFR_Ps8sLlI</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1390,34 +1390,34 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C2ZZh6r6afI</t>
+          <t>DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Moment Your Plans Start Sounding Empty</t>
+          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
+          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1427,34 +1427,34 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>aC9ORClv72g</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1464,34 +1464,34 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>152</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>153</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>81</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TgBjzPpNOwA</t>
+          <t>nvybbwOMwIA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1538,41 +1538,115 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>78</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2OilqvW_HzY</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>6,527</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>6,645</t>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>7,393</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>7,558</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,1188 +465,781 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-19</t>
+          <t>Views_2026-05-21</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-21</t>
+          <t>Views_2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bJKZPpJh1pI</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Moment You STOP, They Take Control</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>2,559</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>2,575</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>The Moment You STOP, They Take Control</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>161</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>lIx_B-vwa8g</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>776</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>783</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2,545</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2,559</t>
+          <t>113</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kRwhF5oBg5w</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>They Don’t Need Your Reasons — They Need Your WEAK SPOT</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kRwhF5oBg5w</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>574</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>578</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>_FYXew5E_Xk</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>hzoRggV72as</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>128</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>130</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08eQH53fdLY</t>
+          <t>z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>When You Move FIRST, They Stop Planning Ahead</t>
+          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=08eQH53fdLY</t>
+          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>88</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>The Moment You REACT, They Know Where To Press</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>q8sgDwcuE0A</t>
+          <t>GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>You OFFER First, So They Stop ASKING</t>
+          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
+          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>vBIa2dW5FJw</t>
+          <t>q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>They Just Insulted You. You Said “Thank You.”</t>
+          <t>You OFFER First, So They Stop ASKING</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>61</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hzoRggV72as</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>They Ignore You Because You Still Let Them Back IN</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>373</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>374</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3XX_s7f_zbk</t>
+          <t>fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>When They Ask "Are You Sure?" — Do This</t>
+          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
+          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>39</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>wus2BJY5Gtk</t>
+          <t>RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Moment You REACT, They Know Where To Press</t>
+          <t>When You WALK AWAY and They Say ONE MORE THING</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
+          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>58</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>s0GGaP5KHU4</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>754</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>755</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>z1Qiw7QvFI0</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>5,896</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>LYoP33V12SU</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Your REACTION Became Their Evidence</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=LYoP33V12SU</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>8fhVxgOWZ84</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>pYH8XAZ8h0A</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>nCKMh-qdDTk</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>You Called It MINOR. They Called It PERMISSION.</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>DTMA3ZRpN08</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>5u_0LFn95ec</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>TgBjzPpNOwA</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>nvybbwOMwIA</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>bMVVPaC5TNc</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2OilqvW_HzY</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>7,393</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>7,558</t>
+          <t>5,961</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-21</t>
+          <t>Views_2026-05-22</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-22</t>
+          <t>Views_2026-05-23</t>
         </is>
       </c>
     </row>
@@ -497,113 +497,113 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,559</t>
+          <t>2,575</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,575</t>
+          <t>2,592</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bJKZPpJh1pI</t>
+          <t>2Hqop6uU8PY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Moment You STOP, They Take Control</t>
+          <t>“So Sensitive?” Here’s the Calm Stoic Response That Ends It</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
+          <t>https://www.youtube.com/watch?v=2Hqop6uU8PY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>48</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>755</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>760</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>vBIa2dW5FJw</t>
+          <t>z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>They Just Insulted You. You Said “Thank You.”</t>
+          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
+          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,71 +613,71 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>783</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>786</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,108 +687,108 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>116</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>The Moment You STOP, They Take Control</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>161</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>164</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hzoRggV72as</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>153</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>156</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pYH8XAZ8h0A</t>
+          <t>q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+          <t>You OFFER First, So They Stop ASKING</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -798,34 +798,34 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>z1Qiw7QvFI0</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -835,12 +835,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>578</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>580</t>
         </is>
       </c>
     </row>
@@ -872,34 +872,34 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>77</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -909,108 +909,108 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>wus2BJY5Gtk</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Moment You REACT, They Know Where To Press</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>97</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>99</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GJJ9OAXIZt8</t>
+          <t>hzoRggV72as</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
+          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
+          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>q8sgDwcuE0A</t>
+          <t>lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>You OFFER First, So They Stop ASKING</t>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1020,34 +1020,34 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DTMA3ZRpN08</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1057,34 +1057,34 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>88</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1094,34 +1094,34 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fAEEc3xxmC8</t>
+          <t>8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
+          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
+          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1131,34 +1131,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RQuIH8Wcqu0</t>
+          <t>cv9HlXnQozI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>When You WALK AWAY and They Say ONE MORE THING</t>
+          <t>The More You Let It Slide, The More They Push You</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
+          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1168,34 +1168,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>87</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>88</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>aC9ORClv72g</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1205,41 +1205,226 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>s0GGaP5KHU4</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>GJJ9OAXIZt8</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>C2ZZh6r6afI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>The Moment Your Plans Start Sounding Empty</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>pYH8XAZ8h0A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>5Ydh9Xglz9s</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>When They Try To Embarrass You, Do This</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>5,896</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>5,961</t>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>6,102</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>6,169</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-22</t>
+          <t>Views_2026-05-23</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-23</t>
+          <t>Views_2026-05-24</t>
         </is>
       </c>
     </row>
@@ -497,76 +497,76 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,575</t>
+          <t>2,592</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,592</t>
+          <t>2,607</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2Hqop6uU8PY</t>
+          <t>bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>“So Sensitive?” Here’s the Calm Stoic Response That Ends It</t>
+          <t>The Moment You STOP, They Take Control</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2Hqop6uU8PY</t>
+          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>164</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>169</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,71 +576,71 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>z1Qiw7QvFI0</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>786</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>789</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -650,367 +650,367 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>116</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>119</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>vBIa2dW5FJw</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>They Just Insulted You. You Said “Thank You.”</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>89</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bJKZPpJh1pI</t>
+          <t>2Hqop6uU8PY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Moment You STOP, They Take Control</t>
+          <t>“So Sensitive?” Here’s the Calm Stoic Response That Ends It</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
+          <t>https://www.youtube.com/watch?v=2Hqop6uU8PY</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>56</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>q8sgDwcuE0A</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>You OFFER First, So They Stop ASKING</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>You OFFER First, So They Stop ASKING</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>63</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>_FYXew5E_Xk</t>
+          <t>lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DTMA3ZRpN08</t>
+          <t>wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
+          <t>The Moment You REACT, They Know Where To Press</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
+          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hzoRggV72as</t>
+          <t>5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
+          <t>When They Try To Embarrass You, Do This</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
+          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>56</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>lIx_B-vwa8g</t>
+          <t>DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
+          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
+          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1020,34 +1020,34 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1057,34 +1057,34 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>372</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>373</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1094,337 +1094,41 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>580</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>581</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8fhVxgOWZ84</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>5,136</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cv9HlXnQozI</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>The More You Let It Slide, The More They Push You</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>aC9ORClv72g</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>s0GGaP5KHU4</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>GJJ9OAXIZt8</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>C2ZZh6r6afI</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>The Moment Your Plans Start Sounding Empty</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>pYH8XAZ8h0A</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>5Ydh9Xglz9s</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>When They Try To Embarrass You, Do This</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>6,102</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>6,169</t>
+          <t>5,181</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,86 +465,86 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-23</t>
+          <t>Views_2026-05-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-24</t>
+          <t>Views_2026-05-25</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,592</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,607</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bJKZPpJh1pI</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Moment You STOP, They Take Control</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>91</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>98</t>
         </is>
       </c>
     </row>
@@ -576,71 +576,71 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>2,607</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>2,612</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>vBIa2dW5FJw</t>
+          <t>bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>They Just Insulted You. You Said “Thank You.”</t>
+          <t>The Moment You STOP, They Take Control</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
+          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -650,219 +650,219 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>169</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>172</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2Hqop6uU8PY</t>
+          <t>lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>“So Sensitive?” Here’s the Calm Stoic Response That Ends It</t>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2Hqop6uU8PY</t>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>81</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>581</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>584</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>789</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>791</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>q8sgDwcuE0A</t>
+          <t>vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You OFFER First, So They Stop ASKING</t>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>121</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>lIx_B-vwa8g</t>
+          <t>q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
+          <t>You OFFER First, So They Stop ASKING</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,34 +872,34 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>64</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>65</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>wus2BJY5Gtk</t>
+          <t>A0x6fkcrix4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Moment You REACT, They Know Where To Press</t>
+          <t>Never Defend Yourself Against Disrespect Here's Why</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
+          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -909,34 +909,34 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>110</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8fhVxgOWZ84</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -946,34 +946,34 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>156</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>157</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5Ydh9Xglz9s</t>
+          <t>DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>When They Try To Embarrass You, Do This</t>
+          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
+          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -983,34 +983,34 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DTMA3ZRpN08</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1020,34 +1020,34 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>374</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>375</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>agifyuQrXW8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1057,34 +1057,34 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>244</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>_yE_ZMKH03Y</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>Stop Overreacting When People Disrespect You – 7 Stoic Rules to Keep Your Calm | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=_yE_ZMKH03Y</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1094,41 +1094,115 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>142</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>143</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>5,136</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>5,181</t>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>6,832</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>6,882</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,108 +465,108 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-24</t>
+          <t>Views_2026-05-25</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-25</t>
+          <t>Views_2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2,612</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2,629</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>89</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>_FYXew5E_Xk</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,71 +576,71 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2,607</t>
+          <t>98</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2,612</t>
+          <t>101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bJKZPpJh1pI</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Moment You STOP, They Take Control</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -650,219 +650,219 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>584</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>587</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>z1Qiw7QvFI0</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lIx_B-vwa8g</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>374</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>376</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>208</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>210</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>99</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>100</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>vBIa2dW5FJw</t>
+          <t>5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>They Just Insulted You. You Said “Thank You.”</t>
+          <t>When They Try To Embarrass You, Do This</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
+          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>q8sgDwcuE0A</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>You OFFER First, So They Stop ASKING</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,34 +872,34 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>375</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>376</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A0x6fkcrix4</t>
+          <t>Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Never Defend Yourself Against Disrespect Here's Why</t>
+          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
+          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -909,300 +909,41 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>72</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>73</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>4,593</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>157</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DTMA3ZRpN08</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>9M1kjkk6oG8</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>agifyuQrXW8</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>_yE_ZMKH03Y</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Stop Overreacting When People Disrespect You – 7 Stoic Rules to Keep Your Calm | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=_yE_ZMKH03Y</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>760</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>761</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>6,832</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>6,882</t>
+          <t>4,643</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,197 +465,197 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-25</t>
+          <t>Views_2026-05-26</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-26</t>
+          <t>Views_2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,612</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,629</t>
+          <t>113</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>_FYXew5E_Xk</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2,629</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2,639</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>791</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>797</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>376</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>381</t>
         </is>
       </c>
     </row>
@@ -687,34 +687,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,34 +724,34 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>761</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>763</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>41_ESKOfX-c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+          <t>If You Don’t Respect Yourself, This Will Happen (Stoic Warning)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+          <t>https://www.youtube.com/watch?v=41_ESKOfX-c</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -761,34 +761,34 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>106</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>108</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>You OFFER First, So They Stop ASKING</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -798,34 +798,34 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5Ydh9Xglz9s</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>When They Try To Embarrass You, Do This</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -835,34 +835,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>102</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,34 +872,34 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>82</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>83</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Um_JjU7jfPo</t>
+          <t>pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -909,41 +909,263 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>131</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>132</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>C19SUX9jC1o</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0a_DUuDQFx0</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>agifyuQrXW8</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>brLELECTtR8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>4,593</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>4,643</t>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>6,898</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>6,957</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,34 +465,34 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-26</t>
+          <t>Views_2026-05-27</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-27</t>
+          <t>Views_2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>_FYXew5E_Xk</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -502,12 +502,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>2,639</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>2,651</t>
         </is>
       </c>
     </row>
@@ -534,150 +534,150 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2,629</t>
+          <t>797</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2,639</t>
+          <t>802</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>The Moment You REACT, They Know Where To Press</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>115</t>
         </is>
       </c>
     </row>
@@ -724,34 +724,34 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>763</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>765</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>41_ESKOfX-c</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>If You Don’t Respect Yourself, This Will Happen (Stoic Warning)</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=41_ESKOfX-c</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -761,34 +761,34 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>588</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>590</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>q8sgDwcuE0A</t>
+          <t>bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>You OFFER First, So They Stop ASKING</t>
+          <t>The Moment You STOP, They Take Control</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
+          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>172</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>173</t>
         </is>
       </c>
     </row>
@@ -835,34 +835,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TgBjzPpNOwA</t>
+          <t>FqpFUsYO-AQ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+          <t>6 Reasons No One Takes You Seriously (Stoic Self-Respect Advice)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+          <t>https://www.youtube.com/watch?v=FqpFUsYO-AQ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,34 +872,34 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>169</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>170</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pYH8XAZ8h0A</t>
+          <t>nvybbwOMwIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -909,34 +909,34 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -946,34 +946,34 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0a_DUuDQFx0</t>
+          <t>hikgGDBJWiU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>When They INTERRUPT You, Don’t Re-Enter Soft</t>
+          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0a_DUuDQFx0</t>
+          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -983,189 +983,41 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>87</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>88</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>agifyuQrXW8</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>5,614</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>245</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>bMVVPaC5TNc</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>brLELECTtR8</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>6,898</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>6,957</t>
+          <t>5,658</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-27</t>
+          <t>Views_2026-05-28</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-28</t>
+          <t>Views_2026-05-30</t>
         </is>
       </c>
     </row>
@@ -497,409 +497,409 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,639</t>
+          <t>2,651</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,651</t>
+          <t>2,684</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>802</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>810</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>wus2BJY5Gtk</t>
+          <t>_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Moment You REACT, They Know Where To Press</t>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>115</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>121</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>_FYXew5E_Xk</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>590</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>596</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>377</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>380</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>106</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bJKZPpJh1pI</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Moment You STOP, They Take Control</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>381</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>384</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FqpFUsYO-AQ</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6 Reasons No One Takes You Seriously (Stoic Self-Respect Advice)</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=FqpFUsYO-AQ</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>102</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>nvybbwOMwIA</t>
+          <t>lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -909,34 +909,34 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fAEEc3xxmC8</t>
+          <t>wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
+          <t>The Moment You REACT, They Know Where To Press</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
+          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -946,34 +946,34 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hikgGDBJWiU</t>
+          <t>hzoRggV72as</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Don’t Explain—This Is When You Should WALK AWAY</t>
+          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hikgGDBJWiU</t>
+          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -983,41 +983,189 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Vye4llkNzwM</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>g54e8p6ylts</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>That “Quick Favor” Is Why They Disrespect You</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=g54e8p6ylts</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>qUd0X0Wn4-s</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>The Calm Response That Stops Rude People Fast</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>5,614</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>5,658</t>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>6,486</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>6,584</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-28</t>
+          <t>Views_2026-05-30</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-30</t>
+          <t>Views_2026-05-31</t>
         </is>
       </c>
     </row>
@@ -497,91 +497,91 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,651</t>
+          <t>2,684</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,684</t>
+          <t>2,703</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>596</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>602</t>
         </is>
       </c>
     </row>
@@ -608,113 +608,113 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>810</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>816</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>_FYXew5E_Xk</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>106</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>109</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>hzoRggV72as</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,34 +724,34 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -761,71 +761,71 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>766</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>769</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>When They Try To Embarrass You, Do This</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>59</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TgBjzPpNOwA</t>
+          <t>s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -835,71 +835,71 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>86</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>lIx_B-vwa8g</t>
+          <t>A0x6fkcrix4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
+          <t>Never Defend Yourself Against Disrespect Here's Why</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
+          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -909,34 +909,34 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>111</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>wus2BJY5Gtk</t>
+          <t>nSSLusuBoC8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Moment You REACT, They Know Where To Press</t>
+          <t>SET BOUNDARIES, GAIN RESPECT: 5 STOIC RULES (For People Who Get WALKED OVER)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
+          <t>https://www.youtube.com/watch?v=nSSLusuBoC8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -946,34 +946,34 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>39</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hzoRggV72as</t>
+          <t>2Hqop6uU8PY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
+          <t>“So Sensitive?” Here’s the Calm Stoic Response That Ends It</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
+          <t>https://www.youtube.com/watch?v=2Hqop6uU8PY</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -983,34 +983,34 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Vye4llkNzwM</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1020,152 +1020,41 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>380</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>381</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>g54e8p6ylts</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>That “Quick Favor” Is Why They Disrespect You</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=g54e8p6ylts</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>5,847</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>38</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>qUd0X0Wn4-s</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>The Calm Response That Stops Rude People Fast</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>766</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>6,486</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>6,584</t>
+          <t>5,909</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-30</t>
+          <t>Views_2026-05-31</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-31</t>
+          <t>Views_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -497,54 +497,54 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,684</t>
+          <t>2,703</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,703</t>
+          <t>2,724</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>816</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>823</t>
         </is>
       </c>
     </row>
@@ -571,54 +571,54 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>602</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>606</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>55</t>
         </is>
       </c>
     </row>
@@ -645,224 +645,224 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>agifyuQrXW8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>245</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>247</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hzoRggV72as</t>
+          <t>pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>132</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>133</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>381</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>382</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5Ydh9Xglz9s</t>
+          <t>TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>When They Try To Embarrass You, Do This</t>
+          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
+          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>86</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>s0GGaP5KHU4</t>
+          <t>Vye4llkNzwM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>When They Ignore Your Point, Don’t RESCUE the Silence</t>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=s0GGaP5KHU4</t>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>lIx_B-vwa8g</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,189 +872,41 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>384</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>385</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A0x6fkcrix4</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Never Defend Yourself Against Disrespect Here's Why</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>5,533</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>111</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>nSSLusuBoC8</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SET BOUNDARIES, GAIN RESPECT: 5 STOIC RULES (For People Who Get WALKED OVER)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=nSSLusuBoC8</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2Hqop6uU8PY</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>“So Sensitive?” Here’s the Calm Stoic Response That Ends It</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=2Hqop6uU8PY</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>5,847</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>5,909</t>
+          <t>5,577</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-05-31</t>
+          <t>Views_2026-06-01</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-01</t>
+          <t>Views_2026-06-02</t>
         </is>
       </c>
     </row>
@@ -497,76 +497,76 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,703</t>
+          <t>2,724</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,724</t>
+          <t>2,739</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>382</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>388</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,337 +576,374 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>59</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>606</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>610</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>agifyuQrXW8</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>823</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>826</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pYH8XAZ8h0A</t>
+          <t>QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>69</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>71</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>133</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>135</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TgBjzPpNOwA</t>
+          <t>_qmVTMUQSDg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+          <t>10 STOIC PHRASES to SILENCE MANIPULATORS (Calm Boundaries)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+          <t>https://www.youtube.com/watch?v=_qmVTMUQSDg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vye4llkNzwM</t>
+          <t>0w4OAOyEEUE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+          <t>When They Interrupt You, Do This in 3 Seconds (Stoic)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+          <t>https://www.youtube.com/watch?v=0w4OAOyEEUE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>135</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>137</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>769</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>771</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>9M1kjkk6oG8</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>5,533</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>5,577</t>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>6,154</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>6,201</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-01</t>
+          <t>Views_2026-06-02</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-02</t>
+          <t>Views_2026-06-03</t>
         </is>
       </c>
     </row>
@@ -497,409 +497,409 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,724</t>
+          <t>2,739</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,739</t>
+          <t>2,753</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>2OilqvW_HzY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>277</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>279</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>826</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>828</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>135</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>137</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>51</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QvJhQNdR-iU</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>251</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>252</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pYH8XAZ8h0A</t>
+          <t>GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>_qmVTMUQSDg</t>
+          <t>lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10 STOIC PHRASES to SILENCE MANIPULATORS (Calm Boundaries)</t>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_qmVTMUQSDg</t>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0w4OAOyEEUE</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>When They Interrupt You, Do This in 3 Seconds (Stoic)</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0w4OAOyEEUE</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>110</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>387</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -909,41 +909,115 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>71</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>72</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>brLELECTtR8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>6,154</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>6,201</t>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>6,435</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-02</t>
+          <t>Views_2026-06-03</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-03</t>
+          <t>Views_2026-06-04</t>
         </is>
       </c>
     </row>
@@ -497,128 +497,128 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,739</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>2,762</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>828</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>835</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2OilqvW_HzY</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>114</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>64</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>67</t>
         </is>
       </c>
     </row>
@@ -650,34 +650,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>137</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>139</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,34 +687,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>772</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>774</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>hzoRggV72as</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,34 +724,34 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GJJ9OAXIZt8</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -761,34 +761,34 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>253</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lIx_B-vwa8g</t>
+          <t>QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
+          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
+          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -798,34 +798,34 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>72</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>73</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -835,34 +835,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>103</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>When They Try To Embarrass You, Do This</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,34 +872,34 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QvJhQNdR-iU</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>387</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>388</t>
         </is>
       </c>
     </row>
@@ -946,78 +946,41 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>611</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>612</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>6,179</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>772</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>6,435</t>
+          <t>6,213</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-03</t>
+          <t>Views_2026-06-04</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-04</t>
+          <t>Views_2026-06-05</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>2,762</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,762</t>
+          <t>2,770</t>
         </is>
       </c>
     </row>
@@ -534,113 +534,113 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>835</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>843</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>612</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>615</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>774</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>776</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pYH8XAZ8h0A</t>
+          <t>TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -650,34 +650,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>88</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,34 +687,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>73</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hzoRggV72as</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,34 +724,34 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -761,34 +761,34 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QvJhQNdR-iU</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -798,34 +798,34 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>104</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -835,152 +835,41 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>122</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5Ydh9Xglz9s</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>When They Try To Embarrass You, Do This</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>5,484</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>9M1kjkk6oG8</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>brLELECTtR8</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>6,179</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>6,213</t>
+          <t>5,513</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-04</t>
+          <t>Views_2026-06-05</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-05</t>
+          <t>Views_2026-06-06</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,762</t>
+          <t>2,770</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,770</t>
+          <t>2,794</t>
         </is>
       </c>
     </row>
@@ -534,113 +534,113 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>843</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>849</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>68</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>88</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TgBjzPpNOwA</t>
+          <t>QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -650,34 +650,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QvJhQNdR-iU</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>615</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>617</t>
         </is>
       </c>
     </row>
@@ -724,34 +724,34 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>The Moment You REACT, They Know Where To Press</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -761,34 +761,34 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -798,34 +798,34 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>388</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>389</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>vBIa2dW5FJw</t>
+          <t>5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>They Just Insulted You. You Said “Thank You.”</t>
+          <t>When They Try To Embarrass You, Do This</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
+          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -835,41 +835,78 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>61</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>776</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>5,484</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>5,513</t>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>5,759</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5,807</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-05</t>
+          <t>Views_2026-06-06</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-06</t>
+          <t>Views_2026-06-07</t>
         </is>
       </c>
     </row>
@@ -497,54 +497,54 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,770</t>
+          <t>2,794</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,794</t>
+          <t>2,802</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>104</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>106</t>
         </is>
       </c>
     </row>
@@ -571,150 +571,150 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>74</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TgBjzPpNOwA</t>
+          <t>nvybbwOMwIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QvJhQNdR-iU</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SIGNS People Don’t Respect You — The Pattern You NORMALIZED</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QvJhQNdR-iU</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>388</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>389</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,189 +724,41 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>617</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>618</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>wus2BJY5Gtk</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Moment You REACT, They Know Where To Press</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>4,110</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9M1kjkk6oG8</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>5Ydh9Xglz9s</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>When They Try To Embarrass You, Do This</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>777</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>5,759</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>5,807</t>
+          <t>4,126</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-06</t>
+          <t>Views_2026-06-07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-07</t>
+          <t>Views_2026-06-08</t>
         </is>
       </c>
     </row>
@@ -497,187 +497,187 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,794</t>
+          <t>2,802</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,802</t>
+          <t>2,811</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>849</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>852</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nvybbwOMwIA</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NOT THAT TONE — The CALM RESPONSE TO DISRESPECT That Ends It FAST (3 Steps)</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nvybbwOMwIA</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>54</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>56</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>618</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>620</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,34 +687,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>106</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>107</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>When They Try To Embarrass You, Do This</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,41 +724,115 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>pYH8XAZ8h0A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>777</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>4,110</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>4,126</t>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>5,482</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>5,505</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-07</t>
+          <t>Views_2026-06-08</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-08</t>
+          <t>Views_2026-06-09</t>
         </is>
       </c>
     </row>
@@ -497,298 +497,298 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,802</t>
+          <t>2,811</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,811</t>
+          <t>2,824</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>56</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>389</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>393</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>778</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>782</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>620</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>623</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5Ydh9Xglz9s</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>When They Try To Embarrass You, Do This</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5Ydh9Xglz9s</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>107</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>109</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pYH8XAZ8h0A</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>852</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>854</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>The Moment You REACT, They Know Where To Press</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -798,41 +798,152 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>hzoRggV72as</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>8pYZtHut-6A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>pYH8XAZ8h0A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>5,482</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>5,505</t>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>6,004</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>6,047</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-08</t>
+          <t>Views_2026-06-09</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-09</t>
+          <t>Views_2026-06-10</t>
         </is>
       </c>
     </row>
@@ -497,76 +497,76 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,811</t>
+          <t>2,824</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,824</t>
+          <t>2,841</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,34 +576,34 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>62</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,182 +613,182 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>854</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>858</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>623</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>626</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>122</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>254</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>110</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>wus2BJY5Gtk</t>
+          <t>bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Moment You REACT, They Know Where To Press</t>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -798,34 +798,34 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>212</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hzoRggV72as</t>
+          <t>2OilqvW_HzY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
+          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
+          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -835,34 +835,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>279</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>280</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,34 +872,34 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>393</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>394</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pYH8XAZ8h0A</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>782</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>783</t>
         </is>
       </c>
     </row>
@@ -933,17 +933,17 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6,004</t>
+          <t>6,595</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6,047</t>
+          <t>6,636</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-09</t>
+          <t>Views_2026-06-10</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-10</t>
+          <t>Views_2026-06-11</t>
         </is>
       </c>
     </row>
@@ -497,76 +497,76 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,824</t>
+          <t>2,841</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,841</t>
+          <t>2,861</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>626</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>634</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,12 +576,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>115</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>120</t>
         </is>
       </c>
     </row>
@@ -608,187 +608,187 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>858</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>863</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>783</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>787</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>_FYXew5E_Xk</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>110</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>113</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>89</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>92</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>When You WALK AWAY and They Say ONE MORE THING</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>58</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -798,34 +798,34 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>122</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>123</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2OilqvW_HzY</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -835,34 +835,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>67</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,34 +872,34 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>51</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>You OFFER First, So They Stop ASKING</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -909,41 +909,337 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>66</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>C2ZZh6r6afI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The Moment Your Plans Start Sounding Empty</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>aC9ORClv72g</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GJJ9OAXIZt8</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DTMA3ZRpN08</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>8fhVxgOWZ84</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>C19SUX9jC1o</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cv9HlXnQozI</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>The More You Let It Slide, The More They Push You</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SnJkoHJPREc</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>The Moment People Start Talking Over You</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>6,595</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>6,636</t>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>6,497</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>6,559</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-10</t>
+          <t>Views_2026-06-11</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-11</t>
+          <t>Views_2026-06-12</t>
         </is>
       </c>
     </row>
@@ -497,298 +497,298 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,841</t>
+          <t>2,861</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,861</t>
+          <t>2,876</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>863</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>868</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>394</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>397</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>634</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>637</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>92</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>The Moment You STOP, They Take Control</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>173</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>174</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RQuIH8Wcqu0</t>
+          <t>GO53yD8kmuY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>When You WALK AWAY and They Say ONE MORE THING</t>
+          <t>13 Signs You're Being DISRESPECTED and Need to Take Action Now</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
+          <t>https://www.youtube.com/watch?v=GO53yD8kmuY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>122</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>_FYXew5E_Xk</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -798,34 +798,34 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>389</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>390</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -835,34 +835,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>256</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>z1Qiw7QvFI0</t>
+          <t>agifyuQrXW8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,374 +872,41 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>248</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>q8sgDwcuE0A</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>You OFFER First, So They Stop ASKING</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>6,069</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>67</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>C2ZZh6r6afI</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>The Moment Your Plans Start Sounding Empty</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>aC9ORClv72g</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>GJJ9OAXIZt8</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>DTMA3ZRpN08</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>8fhVxgOWZ84</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>C19SUX9jC1o</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cv9HlXnQozI</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>The More You Let It Slide, The More They Push You</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>SnJkoHJPREc</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>The Moment People Start Talking Over You</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=SnJkoHJPREc</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>6,497</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>6,559</t>
+          <t>6,103</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-11</t>
+          <t>Views_2026-06-12</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-12</t>
+          <t>Views_2026-06-13</t>
         </is>
       </c>
     </row>
@@ -497,76 +497,76 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,861</t>
+          <t>2,876</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,876</t>
+          <t>2,889</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>637</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>640</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,71 +576,71 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>868</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>871</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>Vye4llkNzwM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>91</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>93</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -650,108 +650,108 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>258</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DTMA3ZRpN08</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>68</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bJKZPpJh1pI</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Moment You STOP, They Take Control</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>397</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>399</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GO53yD8kmuY</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13 Signs You're Being DISRESPECTED and Need to Take Action Now</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GO53yD8kmuY</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>95</t>
         </is>
       </c>
     </row>
@@ -798,34 +798,34 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>390</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>391</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -835,34 +835,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>141</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>142</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>agifyuQrXW8</t>
+          <t>bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,12 +872,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>212</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>213</t>
         </is>
       </c>
     </row>
@@ -896,17 +896,17 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6,069</t>
+          <t>6,030</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6,103</t>
+          <t>6,061</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-12</t>
+          <t>Views_2026-06-13</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-13</t>
+          <t>Views_2026-06-14</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,876</t>
+          <t>2,889</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,889</t>
+          <t>2,915</t>
         </is>
       </c>
     </row>
@@ -534,91 +534,91 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>640</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>647</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vye4llkNzwM</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>399</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>400</t>
         </is>
       </c>
     </row>
@@ -645,268 +645,120 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>259</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>871</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>872</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>787</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>788</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>5,939</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>95</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9M1kjkk6oG8</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>pYH8XAZ8h0A</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>bMVVPaC5TNc</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>6,030</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>6,061</t>
+          <t>5,977</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-13</t>
+          <t>Views_2026-06-14</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-14</t>
+          <t>Views_2026-06-15</t>
         </is>
       </c>
     </row>
@@ -497,39 +497,39 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,889</t>
+          <t>2,915</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,915</t>
+          <t>2,934</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,108 +539,108 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>647</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>651</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>872</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>874</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -650,34 +650,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>96</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>A0x6fkcrix4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>Never Defend Yourself Against Disrespect Here's Why</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,34 +687,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>111</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>112</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>260</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,939</t>
+          <t>4,970</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5,977</t>
+          <t>5,005</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-14</t>
+          <t>Views_2026-06-15</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-15</t>
+          <t>Views_2026-06-16</t>
         </is>
       </c>
     </row>
@@ -497,187 +497,187 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,915</t>
+          <t>2,934</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,934</t>
+          <t>2,970</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>651</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>663</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>874</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>883</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>788</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>792</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>agifyuQrXW8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>248</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>250</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A0x6fkcrix4</t>
+          <t>bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Never Defend Yourself Against Disrespect Here's Why</t>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,34 +687,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>213</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>214</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>142</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>143</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4,970</t>
+          <t>5,850</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5,005</t>
+          <t>5,915</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-15</t>
+          <t>Views_2026-06-16</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-16</t>
+          <t>Views_2026-06-17</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,934</t>
+          <t>2,970</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,970</t>
+          <t>2,986</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>663</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>675</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>883</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>892</t>
         </is>
       </c>
     </row>
@@ -608,39 +608,39 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>792</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>794</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>agifyuQrXW8</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -650,34 +650,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>113</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>115</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,34 +687,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>97</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>98</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pYH8XAZ8h0A</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,41 +724,189 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>71</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>72</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>RQuIH8Wcqu0</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>When You WALK AWAY and They Say ONE MORE THING</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Vye4llkNzwM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5u_0LFn95ec</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A0x6fkcrix4</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Never Defend Yourself Against Disrespect Here's Why</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>5,850</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>5,915</t>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>6,011</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6,058</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-16</t>
+          <t>Views_2026-06-17</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-17</t>
+          <t>Views_2026-06-18</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,970</t>
+          <t>2,986</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2,986</t>
+          <t>3,021</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>675</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>685</t>
         </is>
       </c>
     </row>
@@ -571,39 +571,39 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>892</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>897</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,34 +613,34 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>72</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -650,34 +650,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>794</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>796</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,34 +687,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>214</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>215</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,34 +724,34 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>261</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RQuIH8Wcqu0</t>
+          <t>GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>When You WALK AWAY and They Say ONE MORE THING</t>
+          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
+          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -761,34 +761,34 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Vye4llkNzwM</t>
+          <t>DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -798,115 +798,41 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>5,967</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>158</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A0x6fkcrix4</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Never Defend Yourself Against Disrespect Here's Why</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>6,011</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>6,058</t>
+          <t>6,025</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-17</t>
+          <t>Views_2026-06-18</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-18</t>
+          <t>Views_2026-06-19</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,986</t>
+          <t>3,021</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3,021</t>
+          <t>3,039</t>
         </is>
       </c>
     </row>
@@ -534,76 +534,76 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>685</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>689</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>261</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>264</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>897</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>899</t>
         </is>
       </c>
     </row>
@@ -650,12 +650,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>796</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>798</t>
         </is>
       </c>
     </row>
@@ -687,34 +687,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>216</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>Dt_r6f3nLIQ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>Why No One RESPECTS You — You Keep Making DISRESPECT Cheap</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=Dt_r6f3nLIQ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,34 +724,34 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GJJ9OAXIZt8</t>
+          <t>2OilqvW_HzY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
+          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
+          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -761,78 +761,41 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>280</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>281</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DTMA3ZRpN08</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>6,239</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>5,967</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>6,025</t>
+          <t>6,271</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-18</t>
+          <t>Views_2026-06-19</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-19</t>
+          <t>Views_2026-06-20</t>
         </is>
       </c>
     </row>
@@ -497,39 +497,39 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3,021</t>
+          <t>3,039</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3,039</t>
+          <t>3,052</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>899</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>903</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,108 +576,108 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>689</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>692</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>ZervEMzTJp8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>The Second You Explain Your NO, It Stops Being One</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>aC9ORClv72g</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,34 +687,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dt_r6f3nLIQ</t>
+          <t>qtid1KrxsOg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Why No One RESPECTS You — You Keep Making DISRESPECT Cheap</t>
+          <t>The Real Mistake After DISRESPECT Is Trying to PROVE Yourself</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Dt_r6f3nLIQ</t>
+          <t>https://www.youtube.com/watch?v=qtid1KrxsOg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,34 +724,34 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>58</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2OilqvW_HzY</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -761,41 +761,152 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>391</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>392</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>5u_0LFn95ec</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8yCYD0b2zsM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Why EXPLAINING After DISRESPECT Makes You Look Weaker</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8yCYD0b2zsM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>qUd0X0Wn4-s</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The Calm Response That Stops Rude People Fast</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>6,239</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>6,271</t>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>5,584</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5,612</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-19</t>
+          <t>Views_2026-06-20</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-20</t>
+          <t>Views_2026-06-21</t>
         </is>
       </c>
     </row>
@@ -497,76 +497,76 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3,039</t>
+          <t>3,052</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3,052</t>
+          <t>3,074</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>692</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>698</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,108 +576,108 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>903</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>906</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ZervEMzTJp8</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Second You Explain Your NO, It Stops Being One</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>403</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>aC9ORClv72g</t>
+          <t>hzoRggV72as</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
+          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
+          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8fhVxgOWZ84</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,34 +687,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>74</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>qtid1KrxsOg</t>
+          <t>wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Real Mistake After DISRESPECT Is Trying to PROVE Yourself</t>
+          <t>The Moment You REACT, They Know Where To Press</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qtid1KrxsOg</t>
+          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,34 +724,34 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -761,34 +761,34 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>121</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>The Moment Your Plans Start Sounding Empty</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -798,34 +798,34 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8yCYD0b2zsM</t>
+          <t>aC9ORClv72g</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Why EXPLAINING After DISRESPECT Makes You Look Weaker</t>
+          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8yCYD0b2zsM</t>
+          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -835,34 +835,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>qUd0X0Wn4-s</t>
+          <t>RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Calm Response That Stops Rude People Fast</t>
+          <t>When You WALK AWAY and They Say ONE MORE THING</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -872,41 +872,226 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>bJKZPpJh1pI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>The Moment You STOP, They Take Control</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>UnPmWxqA9Vw</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>This Question Is a Trap: 5 Stoic Rules for Dealing With Manipulators | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UnPmWxqA9Vw</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TgBjzPpNOwA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>5,584</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>5,612</t>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>6,907</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>6,954</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,86 +465,86 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-20</t>
+          <t>Views_2026-06-21</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-21</t>
+          <t>Views_2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3,052</t>
+          <t>698</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3,074</t>
+          <t>701</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>3,074</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>3,077</t>
         </is>
       </c>
     </row>
@@ -576,108 +576,108 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>906</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>909</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hzoRggV72as</t>
+          <t>_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>123</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>124</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>3XX_s7f_zbk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>When They Ask "Are You Sure?" — Do This</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,34 +687,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>69</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>wus2BJY5Gtk</t>
+          <t>vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Moment You REACT, They Know Where To Press</t>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,34 +724,34 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>122</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>123</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>The Moment You STOP, They Take Control</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -761,34 +761,34 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>176</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C2ZZh6r6afI</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Moment Your Plans Start Sounding Empty</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C2ZZh6r6afI</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -798,300 +798,41 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>799</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>800</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>aC9ORClv72g</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>6,041</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RQuIH8Wcqu0</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>When You WALK AWAY and They Say ONE MORE THING</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>bJKZPpJh1pI</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>The Moment You STOP, They Take Control</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>UnPmWxqA9Vw</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>This Question Is a Trap: 5 Stoic Rules for Dealing With Manipulators | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=UnPmWxqA9Vw</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TgBjzPpNOwA</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>798</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>6,907</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>6,954</t>
+          <t>6,056</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -465,49 +465,49 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-21</t>
+          <t>Views_2026-06-22</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-22</t>
+          <t>Views_2026-06-23</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>909</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>915</t>
         </is>
       </c>
     </row>
@@ -534,39 +534,39 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3,074</t>
+          <t>3,077</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3,077</t>
+          <t>3,083</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,12 +576,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>116</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>119</t>
         </is>
       </c>
     </row>
@@ -608,76 +608,76 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>_FYXew5E_Xk</t>
+          <t>2OilqvW_HzY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
+          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
+          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>281</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>283</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3XX_s7f_zbk</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>When They Ask "Are You Sure?" — Do This</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,34 +687,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>403</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>404</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>vBIa2dW5FJw</t>
+          <t>GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>They Just Insulted You. You Said “Thank You.”</t>
+          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
+          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,34 +724,34 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bJKZPpJh1pI</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Moment You STOP, They Take Control</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>701</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>702</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>800</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>801</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>6,041</t>
+          <t>6,397</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6,056</t>
+          <t>6,420</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,219 +465,219 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-22</t>
+          <t>Views_2026-06-23</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-23</t>
+          <t>Views_2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>801</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>803</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3,077</t>
+          <t>98</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3,083</t>
+          <t>99</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>264</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>265</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>FqpFUsYO-AQ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>6 Reasons No One Takes You Seriously (Stoic Self-Respect Advice)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=FqpFUsYO-AQ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>170</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>171</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2OilqvW_HzY</t>
+          <t>bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>216</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>217</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,152 +687,41 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>915</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>916</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GJJ9OAXIZt8</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>2,464</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>brLELECTtR8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>801</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>6,397</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>6,420</t>
+          <t>2,471</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="68" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,219 +465,219 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-23</t>
+          <t>Views_2026-06-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-24</t>
+          <t>Views_2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>3,083</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>3,088</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>803</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>808</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>159</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>163</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FqpFUsYO-AQ</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6 Reasons No One Takes You Seriously (Stoic Self-Respect Advice)</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=FqpFUsYO-AQ</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>404</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>408</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>268</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,41 +687,78 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>124</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>125</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>brLELECTtR8</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2,464</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2,471</t>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5,540</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5,563</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,34 +465,34 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-24</t>
+          <t>Views_2026-06-25</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-25</t>
+          <t>Views_2026-06-26</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -502,263 +502,115 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3,083</t>
+          <t>916</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3,088</t>
+          <t>921</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>3,088</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>3,090</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>_yE_ZMKH03Y</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>Stop Overreacting When People Disrespect You – 7 Stoic Rules to Keep Your Calm | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=_yE_ZMKH03Y</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>143</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>144</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>4,147</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>408</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>C19SUX9jC1o</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>_FYXew5E_Xk</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>brLELECTtR8</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>703</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>5,540</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>5,563</t>
+          <t>4,155</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,152 +465,263 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-25</t>
+          <t>Views_2026-06-26</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-26</t>
+          <t>Views_2026-06-27</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>703</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>709</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3,088</t>
+          <t>78</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3,090</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>_yE_ZMKH03Y</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stop Overreacting When People Disrespect You – 7 Stoic Rules to Keep Your Calm | Stoic Wisdom</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_yE_ZMKH03Y</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>808</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>811</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>mpZoXoLMD3A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>agifyuQrXW8</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>4,147</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>4,155</t>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2,877</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2,894</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,263 +465,152 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-26</t>
+          <t>Views_2026-06-27</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-27</t>
+          <t>Views_2026-06-28</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>392</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>394</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>923</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>925</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>2OilqvW_HzY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>283</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>284</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>1,598</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>923</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>agifyuQrXW8</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2,877</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2,894</t>
+          <t>1,603</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="66" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,34 +465,34 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-27</t>
+          <t>Views_2026-06-28</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-28</t>
+          <t>Views_2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -502,12 +502,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>82</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>84</t>
         </is>
       </c>
     </row>
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>925</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>927</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2OilqvW_HzY</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,41 +576,152 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>268</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>269</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>TgBjzPpNOwA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1,598</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1,603</t>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1,992</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2,000</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-28</t>
+          <t>Views_2026-06-29</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-29</t>
+          <t>Views_2026-06-30</t>
         </is>
       </c>
     </row>
@@ -497,76 +497,76 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>84</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>122</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,34 +576,34 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>125</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>126</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TgBjzPpNOwA</t>
+          <t>bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+          <t>The Moment You STOP, They Take Control</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,34 +613,34 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>176</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>177</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -650,34 +650,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>123</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>124</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>3XX_s7f_zbk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+          <t>When They Ask "Are You Sure?" — Do This</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,41 +687,152 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>71</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>lIx_B-vwa8g</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>qUd0X0Wn4-s</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>The Calm Response That Stops Rude People Fast</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1,992</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2,000</t>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1,207</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1,216</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="68" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-29</t>
+          <t>Views_2026-06-30</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-30</t>
+          <t>Views_2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>409</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>411</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,300 +539,41 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>121</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>122</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>_FYXew5E_Xk</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>529</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>126</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>bJKZPpJh1pI</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>The Moment You STOP, They Take Control</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>vBIa2dW5FJw</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>They Just Insulted You. You Said “Thank You.”</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>3XX_s7f_zbk</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>When They Ask "Are You Sure?" — Do This</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>lIx_B-vwa8g</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>bMVVPaC5TNc</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>qUd0X0Wn4-s</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>The Calm Response That Stops Rude People Fast</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1,207</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1,216</t>
+          <t>532</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="57" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,73 +465,65 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-06-30</t>
+          <t>Views_2026-07-01</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-01</t>
+          <t>Views_2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>927</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>928</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>1</t>
@@ -539,41 +531,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>927</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>121</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>532</t>
+          <t>928</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="57" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,78 +465,152 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-01</t>
+          <t>Views_2026-07-02</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-02</t>
+          <t>Views_2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>269</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>271</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Vye4llkNzwM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>927</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>928</t>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>489</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,34 +465,34 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-02</t>
+          <t>Views_2026-07-03</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-03</t>
+          <t>Views_2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -502,34 +502,34 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>123</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>125</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,78 +539,707 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>411</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>413</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Vye4llkNzwM</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>3,090</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>3,092</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>lIx_B-vwa8g</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>The Moment You LAUGH, Disrespect Gets Permission</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lIx_B-vwa8g</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>vBIa2dW5FJw</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bJKZPpJh1pI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>The Moment You STOP, They Take Control</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>_FYXew5E_Xk</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hzoRggV72as</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>z1Qiw7QvFI0</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>You TURN Too Fast — Now Your Focus Looks Easy to Steal</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=z1Qiw7QvFI0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3XX_s7f_zbk</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>When They Ask "Are You Sure?" — Do This</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>q8sgDwcuE0A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>You OFFER First, So They Stop ASKING</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=q8sgDwcuE0A</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>8fhVxgOWZ84</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>You Said YES Too Soon — Then the Favor Got Bigger</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8fhVxgOWZ84</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ZervEMzTJp8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The Second You Explain Your NO, It Stops Being One</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZervEMzTJp8</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GJJ9OAXIZt8</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DTMA3ZRpN08</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>The Faster You Say YES, the Cheaper Your Time Looks</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DTMA3ZRpN08</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cv9HlXnQozI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>The More You Let It Slide, The More They Push You</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Vye4llkNzwM</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>9M1kjkk6oG8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>UnPmWxqA9Vw</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>This Question Is a Trap: 5 Stoic Rules for Dealing With Manipulators | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UnPmWxqA9Vw</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>489</t>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>5,623</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>5,647</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-04</t>
+          <t>Views_2026-07-05</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-05</t>
+          <t>Views_2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>125</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>128</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>hzoRggV72as</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,41 +539,300 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>wus2BJY5Gtk</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>The Moment You REACT, They Know Where To Press</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>_FYXew5E_Xk</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>8pYZtHut-6A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bJKZPpJh1pI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>The Moment You STOP, They Take Control</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>vBIa2dW5FJw</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>41_ESKOfX-c</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>If You Don’t Respect Yourself, This Will Happen (Stoic Warning)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=41_ESKOfX-c</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>qUd0X0Wn4-s</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>The Calm Response That Stops Rude People Fast</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>576</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>581</t>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1,053</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1,064</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -429,7 +429,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,145 +465,145 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-05</t>
+          <t>Views_2026-07-06</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-06</t>
+          <t>Views_2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>aC9ORClv72g</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hzoRggV72as</t>
+          <t>qUd0X0Wn4-s</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
+          <t>The Calm Response That Stops Rude People Fast</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
+          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>205</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>209</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>wus2BJY5Gtk</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Moment You REACT, They Know Where To Press</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>811</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>813</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>_FYXew5E_Xk</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The More You EXPLAIN, The Weaker Your Answer Sounds</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_FYXew5E_Xk</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,34 +613,34 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>86</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -650,34 +650,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>93</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bJKZPpJh1pI</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Moment You STOP, They Take Control</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,34 +687,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>417</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>418</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>vBIa2dW5FJw</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>They Just Insulted You. You Said “Thank You.”</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -724,34 +724,34 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>128</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>129</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>41_ESKOfX-c</t>
+          <t>bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>If You Don’t Respect Yourself, This Will Happen (Stoic Warning)</t>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=41_ESKOfX-c</t>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -761,34 +761,34 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>220</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>221</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>qUd0X0Wn4-s</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Calm Response That Stops Rude People Fast</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>709</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>710</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1,053</t>
+          <t>2,696</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1,064</t>
+          <t>2,712</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,145 +465,145 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-06</t>
+          <t>Views_2026-07-07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-07</t>
+          <t>Views_2026-07-08</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>aC9ORClv72g</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The SECOND Ask Is Where Your Boundary Gets Tested</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aC9ORClv72g</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>813</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>816</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>qUd0X0Wn4-s</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Calm Response That Stops Rude People Fast</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>418</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>420</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>271</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>272</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>41_ESKOfX-c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>If You Don’t Respect Yourself, This Will Happen (Stoic Warning)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=41_ESKOfX-c</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,34 +613,34 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>109</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>110</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TgBjzPpNOwA</t>
+          <t>agifyuQrXW8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -650,189 +650,41 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>250</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>1,860</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>418</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>bMVVPaC5TNc</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>brLELECTtR8</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>709</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2,696</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2,712</t>
+          <t>1,868</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,108 +465,108 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-07</t>
+          <t>Views_2026-07-08</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-08</t>
+          <t>Views_2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>88</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>395</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>396</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,115 +576,41 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>3,092</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>3,093</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>41_ESKOfX-c</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>If You Don’t Respect Yourself, This Will Happen (Stoic Warning)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=41_ESKOfX-c</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>3,573</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>110</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>agifyuQrXW8</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>If Someone Disrespects You, Do THIS Immediately | Stoic Lessons</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=agifyuQrXW8</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1,860</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1,868</t>
+          <t>3,577</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,34 +465,34 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-08</t>
+          <t>Views_2026-07-09</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-09</t>
+          <t>Views_2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -502,12 +502,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>129</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>131</t>
         </is>
       </c>
     </row>
@@ -534,39 +534,39 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>396</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>398</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,41 +576,78 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3,092</t>
+          <t>272</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3,093</t>
+          <t>273</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>A0x6fkcrix4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Never Defend Yourself Against Disrespect Here's Why</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>3,573</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>3,577</t>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>916</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,108 +465,108 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-09</t>
+          <t>Views_2026-07-10</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-10</t>
+          <t>Views_2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>AB5Tw2Yd4qE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>When Your Point Gets Ignored, Don’t Repeat It—Say This (Stoic Rule)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=AB5Tw2Yd4qE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>164</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>165</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,34 +576,34 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>131</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>132</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A0x6fkcrix4</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Never Defend Yourself Against Disrespect Here's Why</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,41 +613,78 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>3,093</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>3,094</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>mpZoXoLMD3A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>916</t>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4,357</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4,365</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-10</t>
+          <t>Views_2026-07-11</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-11</t>
+          <t>Views_2026-07-12</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AB5Tw2Yd4qE</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>When Your Point Gets Ignored, Don’t Repeat It—Say This (Stoic Rule)</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AB5Tw2Yd4qE</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>710</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>712</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>398</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>399</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,115 +576,41 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>3,094</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>3,095</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3,093</t>
+          <t>4,202</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3,094</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>mpZoXoLMD3A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>928</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>4,357</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>4,365</t>
+          <t>4,206</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,34 +465,34 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-11</t>
+          <t>Views_2026-07-12</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-12</t>
+          <t>Views_2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -502,71 +502,71 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>420</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>422</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>929</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>931</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,41 +576,115 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3,094</t>
+          <t>165</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3,095</t>
+          <t>166</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>C19SUX9jC1o</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2OilqvW_HzY</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>4,202</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>4,206</t>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2,071</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2,078</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="66" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,108 +465,108 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-12</t>
+          <t>Views_2026-07-13</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-13</t>
+          <t>Views_2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>274</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>277</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>422</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>425</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,34 +576,34 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>132</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>133</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>AB5Tw2Yd4qE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>When Your Point Gets Ignored, Don’t Repeat It—Say This (Stoic Rule)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=AB5Tw2Yd4qE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,34 +613,34 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2OilqvW_HzY</t>
+          <t>nSSLusuBoC8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+          <t>SET BOUNDARIES, GAIN RESPECT: 5 STOIC RULES (For People Who Get WALKED OVER)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+          <t>https://www.youtube.com/watch?v=nSSLusuBoC8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -650,41 +650,226 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>TH331d5OGVs</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Disrespected in a Meeting? Do This (Stoic 30-Second Rule)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TH331d5OGVs</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1A1bXruIgD4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Disrespected? These 10 Manipulative Phrases Make You Apologize (Stoic Replies)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1A1bXruIgD4</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>zOkGHnsmORY</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3,095</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3,096</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mpZoXoLMD3A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>932</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2,071</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2,078</t>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5,871</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>5,885</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,108 +465,108 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-13</t>
+          <t>Views_2026-07-14</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-14</t>
+          <t>Views_2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>220</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>222</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>3,096</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>3,098</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,300 +576,41 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>425</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>426</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AB5Tw2Yd4qE</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>When Your Point Gets Ignored, Don’t Repeat It—Say This (Stoic Rule)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=AB5Tw2Yd4qE</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-01-04</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>3,741</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>nSSLusuBoC8</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SET BOUNDARIES, GAIN RESPECT: 5 STOIC RULES (For People Who Get WALKED OVER)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=nSSLusuBoC8</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TH331d5OGVs</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Disrespected in a Meeting? Do This (Stoic 30-Second Rule)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=TH331d5OGVs</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2025-12-25</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1A1bXruIgD4</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Disrespected? These 10 Manipulative Phrases Make You Apologize (Stoic Replies)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=1A1bXruIgD4</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2025-12-24</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>zOkGHnsmORY</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>3,095</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3,096</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mpZoXoLMD3A</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>932</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>816</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>817</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>5,871</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>5,885</t>
+          <t>3,746</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,108 +465,108 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-14</t>
+          <t>Views_2026-07-15</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-15</t>
+          <t>Views_2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bMVVPaC5TNc</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>People Don’t Respect You? Stop Doing These 5 Things | Stoic Wisdom</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bMVVPaC5TNc</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>277</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>278</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3,096</t>
+          <t>133</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3,098</t>
+          <t>134</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,41 +576,78 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>712</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>713</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>3,741</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>3,746</t>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1,939</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1,943</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,108 +465,108 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-15</t>
+          <t>Views_2026-07-16</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-16</t>
+          <t>Views_2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>3,098</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>3,106</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>426</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>428</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,34 +576,34 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>134</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>135</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,41 +613,78 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>713</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>714</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>mpZoXoLMD3A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1,939</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1,943</t>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5,303</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5,316</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,49 +465,49 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-16</t>
+          <t>Views_2026-07-17</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-17</t>
+          <t>Views_2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3,098</t>
+          <t>933</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3,106</t>
+          <t>937</t>
         </is>
       </c>
     </row>
@@ -539,71 +539,71 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>428</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>430</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>3,106</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>3,108</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,34 +613,34 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>279</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -650,41 +650,78 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>714</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>715</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>5,303</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>5,316</t>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>6,277</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>6,288</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,263 +465,115 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-17</t>
+          <t>Views_2026-07-18</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-18</t>
+          <t>Views_2026-07-19</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>430</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>432</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>3,108</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>3,109</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3,106</t>
+          <t>3,538</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3,108</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>C19SUX9jC1o</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>brLELECTtR8</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>714</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>818</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>819</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>6,277</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>6,288</t>
+          <t>3,541</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,115 +465,189 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-18</t>
+          <t>Views_2026-07-19</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-19</t>
+          <t>Views_2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>819</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>830</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3,108</t>
+          <t>432</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3,109</t>
+          <t>434</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Um_JjU7jfPo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mpZoXoLMD3A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>3,538</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>3,541</t>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2,261</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2,276</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,49 +465,49 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-19</t>
+          <t>Views_2026-07-20</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-20</t>
+          <t>Views_2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>938</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>940</t>
         </is>
       </c>
     </row>
@@ -534,120 +534,46 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>434</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>435</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Um_JjU7jfPo</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>1,372</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>mpZoXoLMD3A</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2,261</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2,276</t>
+          <t>1,375</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -465,49 +465,49 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-20</t>
+          <t>Views_2026-07-21</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-21</t>
+          <t>Views_2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>126</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>127</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>435</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>436</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1,372</t>
+          <t>561</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1,375</t>
+          <t>563</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-21</t>
+          <t>Views_2026-07-22</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-22</t>
+          <t>Views_2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>vBIa2dW5FJw</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>They Just Insulted You. You Said “Thank You.”</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>135</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>137</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,41 +539,189 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>166</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>167</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>C19SUX9jC1o</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>brLELECTtR8</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mpZoXoLMD3A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>563</t>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2,671</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2,678</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-22</t>
+          <t>Views_2026-07-23</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-23</t>
+          <t>Views_2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>167</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>168</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>280</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>281</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,152 +576,41 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>437</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>438</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>884</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>437</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>brLELECTtR8</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>mpZoXoLMD3A</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2,671</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2,678</t>
+          <t>887</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-23</t>
+          <t>Views_2026-07-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-24</t>
+          <t>Views_2026-07-25</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>137</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>139</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>438</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>439</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,12 +576,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>941</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>942</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>1,516</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>1,520</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-24</t>
+          <t>Views_2026-07-25</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-25</t>
+          <t>Views_2026-07-26</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>127</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>128</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -576,12 +576,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>942</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>943</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1,516</t>
+          <t>1,110</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1,520</t>
+          <t>1,113</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-25</t>
+          <t>Views_2026-07-26</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-26</t>
+          <t>Views_2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>vBIa2dW5FJw</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>They Just Insulted You. You Said “Thank You.”</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>168</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>171</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fAEEc3xxmC8</t>
+          <t>uyK1jiL9Hek</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>STOP EXPLAINING Your Decisions to People Who Keep Pushing</t>
+          <t>Why One INSULT Can Ruin Your Entire Day</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fAEEc3xxmC8</t>
+          <t>https://www.youtube.com/watch?v=uyK1jiL9Hek</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,41 +576,78 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>439</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>440</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>831</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1,110</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1,113</t>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1,465</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1,471</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,34 +465,34 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-26</t>
+          <t>Views_2026-07-27</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-27</t>
+          <t>Views_2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -502,34 +502,34 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>831</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>834</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>uyK1jiL9Hek</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why One INSULT Can Ruin Your Entire Day</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uyK1jiL9Hek</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>171</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>172</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,78 +576,41 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>281</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>282</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>1,283</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>831</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1,465</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1,471</t>
+          <t>1,288</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,73 +465,65 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-27</t>
+          <t>Views_2026-07-28</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-28</t>
+          <t>Views_2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>139</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>140</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>1</t>
@@ -539,78 +531,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>139</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>172</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C19SUX9jC1o</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1,283</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1,288</t>
+          <t>140</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,78 +465,115 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-28</t>
+          <t>Views_2026-07-29</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-29</t>
+          <t>Views_2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>440</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>442</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>GO53yD8kmuY</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13 Signs You're Being DISRESPECTED and Need to Take Action Now</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GO53yD8kmuY</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>140</t>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>565</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-29</t>
+          <t>Views_2026-07-30</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-30</t>
+          <t>Views_2026-07-31</t>
         </is>
       </c>
     </row>
@@ -497,83 +497,194 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>442</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>446</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GO53yD8kmuY</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13 Signs You're Being DISRESPECTED and Need to Take Action Now</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GO53yD8kmuY</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>716</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>718</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Um_JjU7jfPo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>834</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>562</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>565</t>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2,206</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2,216</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-30</t>
+          <t>Views_2026-07-31</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-31</t>
+          <t>Views_2026-08-01</t>
         </is>
       </c>
     </row>
@@ -497,194 +497,83 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>446</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>449</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>172</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>173</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>618</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>142</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Um_JjU7jfPo</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Why RUSHING to Fill Silence Makes You Lose PRESENCE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Um_JjU7jfPo</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>834</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>835</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2,206</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2,216</t>
+          <t>622</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-07-31</t>
+          <t>Views_2026-08-01</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-01</t>
+          <t>Views_2026-08-02</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>brLELECTtR8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>718</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>719</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,41 +539,78 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>943</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>944</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>622</t>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2,496</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2,499</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-01</t>
+          <t>Views_2026-08-02</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-02</t>
+          <t>Views_2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>brLELECTtR8</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4 Habits That Destroy Your Self-Respect (Stop These First) | Stoicism | Stoic Lessons</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=brLELECTtR8</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>449</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>451</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,78 +539,41 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>836</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>837</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>1,285</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>836</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2,496</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2,499</t>
+          <t>1,288</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -465,49 +465,49 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-02</t>
+          <t>Views_2026-08-03</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-03</t>
+          <t>Views_2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>88</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>89</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>837</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>838</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1,285</t>
+          <t>925</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1,288</t>
+          <t>927</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,115 +465,152 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-03</t>
+          <t>Views_2026-08-04</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-04</t>
+          <t>Views_2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>173</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>175</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>451</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>453</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>C19SUX9jC1o</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>927</t>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>911</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,152 +465,78 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-04</t>
+          <t>Views_2026-08-05</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-05</t>
+          <t>Views_2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>453</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>457</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>453</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>453</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C19SUX9jC1o</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>906</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>911</t>
+          <t>457</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,78 +465,263 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-05</t>
+          <t>Views_2026-08-06</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-06</t>
+          <t>Views_2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>A0x6fkcrix4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>Never Defend Yourself Against Disrespect Here's Why</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>117</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>mpZoXoLMD3A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DRQBvtISgH8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Public Humiliation Only Works If You React</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>nCKMh-qdDTk</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>zOkGHnsmORY</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3,109</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3,110</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>838</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>453</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>457</t>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5,146</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>5,155</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,263 +465,78 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-06</t>
+          <t>Views_2026-08-07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-07</t>
+          <t>Views_2026-08-08</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A0x6fkcrix4</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Never Defend Yourself Against Disrespect Here's Why</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>457</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>458</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>457</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>946</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DRQBvtISgH8</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Public Humiliation Only Works If You React</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=DRQBvtISgH8</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>nCKMh-qdDTk</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>zOkGHnsmORY</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>3,109</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>3,110</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>838</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>839</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>5,146</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>5,155</t>
+          <t>458</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-07</t>
+          <t>Views_2026-08-08</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-08</t>
+          <t>Views_2026-08-09</t>
         </is>
       </c>
     </row>
@@ -497,46 +497,83 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>458</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>460</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>A0x6fkcrix4</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Never Defend Yourself Against Disrespect Here's Why</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>457</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>458</t>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>578</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-08</t>
+          <t>Views_2026-08-09</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-09</t>
+          <t>Views_2026-08-10</t>
         </is>
       </c>
     </row>
@@ -497,83 +497,194 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>460</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>465</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A0x6fkcrix4</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Never Defend Yourself Against Disrespect Here's Why</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A0x6fkcrix4</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>93</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>zOkGHnsmORY</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3,110</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3,112</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mpZoXoLMD3A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>578</t>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4,748</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4,760</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-09</t>
+          <t>Views_2026-08-10</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-10</t>
+          <t>Views_2026-08-11</t>
         </is>
       </c>
     </row>
@@ -497,194 +497,83 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>465</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>467</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>3,112</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>3,113</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3,110</t>
+          <t>3,577</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3,112</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>mpZoXoLMD3A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>4,748</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>4,760</t>
+          <t>3,580</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-10</t>
+          <t>Views_2026-08-11</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-11</t>
+          <t>Views_2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>That “Small” Disrespect Teaches People How to Treat You</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>93</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,41 +539,78 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3,112</t>
+          <t>175</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3,113</t>
+          <t>176</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>467</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>3,577</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>3,580</t>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>738</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -429,7 +429,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-11</t>
+          <t>Views_2026-08-12</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-12</t>
+          <t>Views_2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nCKMh-qdDTk</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>That “Small” Disrespect Teaches People How to Treat You</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nCKMh-qdDTk</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>468</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>473</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>283</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>284</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,12 +576,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>839</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>840</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>1,590</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>1,597</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -429,7 +429,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-12</t>
+          <t>Views_2026-08-13</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-13</t>
+          <t>Views_2026-08-14</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>473</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>477</t>
         </is>
       </c>
     </row>
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>284</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>285</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>zOkGHnsmORY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,12 +576,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>3,113</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>3,114</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1,590</t>
+          <t>3,870</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1,597</t>
+          <t>3,876</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-13</t>
+          <t>Views_2026-08-14</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-14</t>
+          <t>Views_2026-08-15</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>477</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>480</t>
         </is>
       </c>
     </row>
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>285</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>286</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>zOkGHnsmORY</t>
+          <t>_qmVTMUQSDg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Handling Disrespect: 7 Situations Where Silence Is Real Power | Stoic Wisdom</t>
+          <t>10 STOIC PHRASES to SILENCE MANIPULATORS (Calm Boundaries)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zOkGHnsmORY</t>
+          <t>https://www.youtube.com/watch?v=_qmVTMUQSDg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,41 +576,115 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3,113</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3,114</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>FqpFUsYO-AQ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>6 Reasons No One Takes You Seriously (Stoic Self-Respect Advice)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FqpFUsYO-AQ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2OilqvW_HzY</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>3,870</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>3,876</t>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1,248</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1,255</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="66" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-14</t>
+          <t>Views_2026-08-15</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-15</t>
+          <t>Views_2026-08-16</t>
         </is>
       </c>
     </row>
@@ -497,41 +497,33 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>480</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>481</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>1</t>
@@ -539,152 +531,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>480</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>286</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>_qmVTMUQSDg</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>10 STOIC PHRASES to SILENCE MANIPULATORS (Calm Boundaries)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=_qmVTMUQSDg</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>FqpFUsYO-AQ</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>6 Reasons No One Takes You Seriously (Stoic Self-Respect Advice)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=FqpFUsYO-AQ</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2OilqvW_HzY</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1,248</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1,255</t>
+          <t>481</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-15</t>
+          <t>Views_2026-08-16</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-16</t>
+          <t>Views_2026-08-17</t>
         </is>
       </c>
     </row>
@@ -497,46 +497,83 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>481</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>483</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>2OilqvW_HzY</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>481</t>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>771</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -429,7 +429,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="66" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-16</t>
+          <t>Views_2026-08-17</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-17</t>
+          <t>Views_2026-08-18</t>
         </is>
       </c>
     </row>
@@ -497,54 +497,54 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>483</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>484</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2OilqvW_HzY</t>
+          <t>mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>947</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>948</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>1,430</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>1,432</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-17</t>
+          <t>Views_2026-08-18</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-18</t>
+          <t>Views_2026-08-19</t>
         </is>
       </c>
     </row>
@@ -497,83 +497,46 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>484</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>486</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mpZoXoLMD3A</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>They Disrespect You to Get a Reaction — Do This Instead</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=mpZoXoLMD3A</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>484</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>948</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1,430</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1,432</t>
+          <t>486</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,78 +465,115 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-18</t>
+          <t>Views_2026-08-19</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-19</t>
+          <t>Views_2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>399</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>400</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>486</t>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>885</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>887</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="57" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,34 +465,34 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-19</t>
+          <t>Views_2026-08-20</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-20</t>
+          <t>Views_2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -502,34 +502,34 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>176</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>177</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,41 +539,78 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>143</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>144</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>9M1kjkk6oG8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>885</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>887</t>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>722</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -429,7 +429,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="57" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,34 +465,34 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-20</t>
+          <t>Views_2026-08-21</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-21</t>
+          <t>Views_2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>How to Win People’s RESPECT Before You Say a Word</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -502,34 +502,34 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>64</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>65</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pYH8XAZ8h0A</t>
+          <t>C19SUX9jC1o</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>STOP TOLERATING DISRESPECT — Set the Line Without Drama</t>
+          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pYH8XAZ8h0A</t>
+          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>286</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>287</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9M1kjkk6oG8</t>
+          <t>Vye4llkNzwM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Why People DISRESPECT You (You Made It SAFE)</t>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9M1kjkk6oG8</t>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,12 +576,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>96</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>97</t>
         </is>
       </c>
     </row>
@@ -605,12 +605,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>446</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>449</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,34 +465,34 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-21</t>
+          <t>Views_2026-08-22</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-22</t>
+          <t>Views_2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cxx0wy3mYzA</t>
+          <t>hzoRggV72as</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>How to Win People’s RESPECT Before You Say a Word</t>
+          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Cxx0wy3mYzA</t>
+          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -502,34 +502,34 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C19SUX9jC1o</t>
+          <t>wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WALK AWAY When Disrespected (When Walking Away Is POWER)</t>
+          <t>The Moment You REACT, They Know Where To Press</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=C19SUX9jC1o</t>
+          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Vye4llkNzwM</t>
+          <t>vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+          <t>They Just Insulted You. You Said “Thank You.”</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,41 +576,78 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>128</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>129</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>446</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>449</t>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>685</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,189 +465,115 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-22</t>
+          <t>Views_2026-08-23</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-23</t>
+          <t>Views_2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hzoRggV72as</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ignored Again? Stop Reopening the Door | Stoic Boundary</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=hzoRggV72as</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>143</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>145</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>wus2BJY5Gtk</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Moment You REACT, They Know Where To Press</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wus2BJY5Gtk</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>488</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>490</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>vBIa2dW5FJw</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>They Just Insulted You. You Said “Thank You.”</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=vBIa2dW5FJw</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>631</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>129</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>685</t>
+          <t>635</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,115 +465,152 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-23</t>
+          <t>Views_2026-08-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-24</t>
+          <t>Views_2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>8pYZtHut-6A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>You’re Too EASY to Reach — That’s the Problem</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>123</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>124</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>Vye4llkNzwM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>97</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>98</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>635</t>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>368</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -429,7 +429,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="61" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-24</t>
+          <t>Views_2026-08-25</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-25</t>
+          <t>Views_2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8pYZtHut-6A</t>
+          <t>TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>You’re Too EASY to Reach — That’s the Problem</t>
+          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8pYZtHut-6A</t>
+          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>94</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Vye4llkNzwM</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stop Overreacting — Do This Before You Speak (5 Stoic Rules) | Stoic Wisdom</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Vye4llkNzwM</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>490</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>491</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>-vU8JsRIpLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>Disrespected? Use the 3-Second Stoic Rule (Marcus Aurelius)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=-vU8JsRIpLA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,12 +576,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>101</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>684</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>688</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="61" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-25</t>
+          <t>Views_2026-08-26</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-26</t>
+          <t>Views_2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TgBjzPpNOwA</t>
+          <t>RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Rule of the 3 Silences (Most People Never Learn This)</t>
+          <t>When You WALK AWAY and They Say ONE MORE THING</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TgBjzPpNOwA</t>
+          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>62</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,78 +539,41 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>840</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>841</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-vU8JsRIpLA</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Disrespected? Use the 3-Second Stoic Rule (Marcus Aurelius)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-vU8JsRIpLA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>902</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>101</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>688</t>
+          <t>904</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-26</t>
+          <t>Views_2026-08-27</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-27</t>
+          <t>Views_2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RQuIH8Wcqu0</t>
+          <t>5u_0LFn95ec</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>When You WALK AWAY and They Say ONE MORE THING</t>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>177</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>179</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7dzAj6kW8oM</t>
+          <t>y_HfwluuNI8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>When Someone Disrespects You, Say This (5 Stoic Responses)</t>
+          <t>You Said NO — Then You Ruined It</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7dzAj6kW8oM</t>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,41 +539,189 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>99</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>100</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>bJKZPpJh1pI</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>The Moment You STOP, They Take Control</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3XX_s7f_zbk</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>When They Ask "Are You Sure?" — Do This</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RQuIH8Wcqu0</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When You WALK AWAY and They Say ONE MORE THING</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>902</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>904</t>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1,081</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1,088</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="61" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,34 +465,34 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-27</t>
+          <t>Views_2026-08-29</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-29</t>
+          <t>Views_2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -502,34 +502,34 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>492</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>494</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>cv9HlXnQozI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>The More You Let It Slide, The More They Push You</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>91</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bJKZPpJh1pI</t>
+          <t>GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Moment You STOP, They Take Control</t>
+          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
+          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,34 +576,34 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3XX_s7f_zbk</t>
+          <t>khBEVHIzKEM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>When They Ask "Are You Sure?" — Do This</t>
+          <t>Why Being YOURSELF Is Keeping You STUCK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3XX_s7f_zbk</t>
+          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -613,34 +613,34 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>122</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>123</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RQuIH8Wcqu0</t>
+          <t>-vU8JsRIpLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>When You WALK AWAY and They Say ONE MORE THING</t>
+          <t>Disrespected? Use the 3-Second Stoic Rule (Marcus Aurelius)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RQuIH8Wcqu0</t>
+          <t>https://www.youtube.com/watch?v=-vU8JsRIpLA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -650,34 +650,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>102</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>B5ip0KwwVig</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>How To Command Respect As A Quiet Man | Stoic Wisdom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=B5ip0KwwVig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,41 +687,78 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>56</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>qUd0X0Wn4-s</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>The Calm Response That Stops Rude People Fast</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1,081</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>1,088</t>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1,105</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1,113</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="61" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-29</t>
+          <t>Views_2026-08-30</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-30</t>
+          <t>Views_2026-08-31</t>
         </is>
       </c>
     </row>
@@ -497,41 +497,33 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>494</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>495</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cv9HlXnQozI</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The More You Let It Slide, The More They Push You</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=cv9HlXnQozI</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>1</t>
@@ -539,226 +531,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>494</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>91</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>GJJ9OAXIZt8</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>You Become Their BACKUP Plan When You Answer Too Fast</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=GJJ9OAXIZt8</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>khBEVHIzKEM</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Why Being YOURSELF Is Keeping You STUCK</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=khBEVHIzKEM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>-vU8JsRIpLA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Disrespected? Use the 3-Second Stoic Rule (Marcus Aurelius)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-vU8JsRIpLA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>B5ip0KwwVig</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>How To Command Respect As A Quiet Man | Stoic Wisdom</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=B5ip0KwwVig</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>qUd0X0Wn4-s</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>The Calm Response That Stops Rude People Fast</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=qUd0X0Wn4-s</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>1,105</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>1,113</t>
+          <t>495</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-30</t>
+          <t>Views_2026-08-31</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-31</t>
+          <t>Views_2026-09-01</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>495</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>498</t>
         </is>
       </c>
     </row>
@@ -526,17 +526,17 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>495</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>498</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -429,7 +429,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,49 +465,49 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-08-31</t>
+          <t>Views_2026-09-01</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-01</t>
+          <t>Views_2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>2OilqvW_HzY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>288</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>289</t>
         </is>
       </c>
     </row>
@@ -526,17 +526,17 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>288</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>289</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="66" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,78 +465,115 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-01</t>
+          <t>Views_2026-09-02</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-02</t>
+          <t>Views_2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2OilqvW_HzY</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Why Silence &amp; Walking Away Beat Every Disrespect (3 Stoic Rules)</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2OilqvW_HzY</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>498</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>501</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>y_HfwluuNI8</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>You Said NO — Then You Ruined It</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>289</t>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>602</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -465,12 +465,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-02</t>
+          <t>Views_2026-09-03</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-03</t>
+          <t>Views_2026-09-05</t>
         </is>
       </c>
     </row>
@@ -497,39 +497,39 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>501</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>510</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>y_HfwluuNI8</t>
+          <t>bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>You Said NO — Then You Ruined It</t>
+          <t>The Moment You STOP, They Take Control</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y_HfwluuNI8</t>
+          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,41 +539,78 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>181</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>5u_0LFn95ec</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>🔥 TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>602</t>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>871</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -429,7 +429,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,71 +465,71 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-03</t>
+          <t>Views_2026-09-05</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-05</t>
+          <t>Views_2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>D24CWt5ahQA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>146</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>147</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bJKZPpJh1pI</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Moment You STOP, They Take Control</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bJKZPpJh1pI</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,34 +539,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>510</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>511</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5u_0LFn95ec</t>
+          <t>-gHiXrx2ie4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Why DISRESPECT Repeats When You Don’t Walk Away</t>
+          <t>How to Gain Respect Without Acting Fake or Aggressive | Stoic Lessons</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5u_0LFn95ec</t>
+          <t>https://www.youtube.com/watch?v=-gHiXrx2ie4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -576,12 +576,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>717</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>720</t>
         </is>
       </c>
     </row>

--- a/report_views_increased.xlsx
+++ b/report_views_increased.xlsx
@@ -425,11 +425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="61" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -465,34 +465,34 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-05</t>
+          <t>Views_2026-09-06</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Views_2026-09-06</t>
+          <t>Views_2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D24CWt5ahQA</t>
+          <t>8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>When They JOKE AT YOUR EXPENSE, Say This (Stoic Boundary)</t>
+          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=D24CWt5ahQA</t>
+          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -502,34 +502,34 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>511</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>512</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8bZc3UMmGkg</t>
+          <t>-vU8JsRIpLA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>If They Reply With One Word, Do This (Stoic Texting Rule)</t>
+          <t>Disrespected? Use the 3-Second Stoic Rule (Marcus Aurelius)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8bZc3UMmGkg</t>
+          <t>https://www.youtube.com/watch?v=-vU8JsRIpLA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -539,78 +539,41 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>103</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-gHiXrx2ie4</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>How to Gain Respect Without Acting Fake or Aggressive | Stoic Lessons</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=-gHiXrx2ie4</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2025-12-06</t>
-        </is>
-      </c>
+          <t>🔥 TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>613</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>🔥 TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>720</t>
+          <t>615</t>
         </is>
       </c>
     </row>
